--- a/docs/use_cases_source/AI Transformation Plan (Prod) E&E.xlsx
+++ b/docs/use_cases_source/AI Transformation Plan (Prod) E&E.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Production\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jengza\Desktop\use_case_web\docs\use_cases_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BC82D3-3CB9-4497-AE68-84B8FBE3B04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A86D83-DF0A-4AB4-A3D8-C97499A37C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" firstSheet="4" activeTab="7" xr2:uid="{703667DF-10EA-481F-B479-3CB23F3CF2AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" firstSheet="4" activeTab="4" xr2:uid="{703667DF-10EA-481F-B479-3CB23F3CF2AB}"/>
   </bookViews>
   <sheets>
     <sheet name="AI-Transform-Plan" sheetId="2" state="hidden" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="403">
   <si>
     <t>AI Transformation Plan</t>
   </si>
@@ -126,7 +126,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -136,7 +136,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -146,7 +146,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -156,7 +156,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -166,7 +166,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -183,7 +183,7 @@
         <i/>
         <sz val="14"/>
         <color theme="4" tint="0.39997558519241921"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -194,7 +194,7 @@
         <b/>
         <sz val="14"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -222,7 +222,7 @@
         <b/>
         <sz val="11"/>
         <color theme="8" tint="0.39997558519241921"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -233,7 +233,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -249,7 +249,7 @@
         <b/>
         <sz val="11"/>
         <color theme="8" tint="0.39997558519241921"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -260,7 +260,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -282,7 +282,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2119,7 +2119,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2129,7 +2129,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2140,7 +2140,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2150,7 +2150,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2168,7 +2168,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2183,7 +2183,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2194,7 +2194,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2204,7 +2204,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2231,7 +2231,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2246,7 +2246,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2261,7 +2261,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2276,7 +2276,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2291,7 +2291,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2302,7 +2302,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2321,7 +2321,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2331,7 +2331,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2448,7 +2448,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2463,7 +2463,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2474,7 +2474,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2484,7 +2484,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2499,7 +2499,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2514,7 +2514,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2545,7 +2545,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2953,22 +2953,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="187" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="188" formatCode="0.0%"/>
+    <numFmt numFmtId="189" formatCode="0.0"/>
   </numFmts>
   <fonts count="81">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2976,7 +2976,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2984,7 +2984,7 @@
       <b/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2992,14 +2992,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3007,7 +3007,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3016,7 +3016,7 @@
       <i/>
       <sz val="14"/>
       <color theme="4" tint="0.39997558519241921"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3024,7 +3024,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3032,7 +3032,7 @@
       <b/>
       <sz val="11"/>
       <color theme="8" tint="0.39997558519241921"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3040,7 +3040,7 @@
       <b/>
       <sz val="11"/>
       <color theme="4" tint="0.39997558519241921"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3048,28 +3048,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="5" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3396,7 +3396,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3404,7 +3404,7 @@
       <b/>
       <sz val="13.5"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3419,7 +3419,7 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3456,7 +3456,7 @@
       <u/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3465,7 +3465,7 @@
       <u/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3511,7 +3511,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3520,7 +3520,7 @@
       <u/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4620,7 +4620,7 @@
     <xf numFmtId="9" fontId="44" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="42" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5058,6 +5058,114 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="189" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5073,9 +5181,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5094,111 +5199,6 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5208,6 +5208,120 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5227,130 +5341,43 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="35" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="35" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="35" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="55" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="189" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5363,33 +5390,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5538,8 +5538,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="21664098" y="909872"/>
-          <a:ext cx="553401" cy="832255"/>
+          <a:off x="23988198" y="909872"/>
+          <a:ext cx="648651" cy="832255"/>
           <a:chOff x="187" y="113"/>
           <a:chExt cx="74" cy="1980"/>
         </a:xfrm>
@@ -5660,8 +5660,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="23311117" y="897967"/>
-          <a:ext cx="635931" cy="832798"/>
+          <a:off x="25825717" y="897967"/>
+          <a:ext cx="683556" cy="832798"/>
           <a:chOff x="406" y="112"/>
           <a:chExt cx="77" cy="58"/>
         </a:xfrm>
@@ -5792,8 +5792,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="24124834" y="890447"/>
-          <a:ext cx="504654" cy="833288"/>
+          <a:off x="26687059" y="890447"/>
+          <a:ext cx="552279" cy="833288"/>
           <a:chOff x="887" y="110"/>
           <a:chExt cx="42" cy="51"/>
         </a:xfrm>
@@ -5914,8 +5914,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="24816385" y="852487"/>
-          <a:ext cx="465988" cy="867109"/>
+          <a:off x="27473860" y="852487"/>
+          <a:ext cx="513613" cy="867109"/>
           <a:chOff x="959" y="110"/>
           <a:chExt cx="41" cy="59"/>
         </a:xfrm>
@@ -6036,8 +6036,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="25506868" y="1195248"/>
-          <a:ext cx="693412" cy="524885"/>
+          <a:off x="28211968" y="1195248"/>
+          <a:ext cx="741037" cy="524885"/>
           <a:chOff x="1002" y="126"/>
           <a:chExt cx="61" cy="893"/>
         </a:xfrm>
@@ -6156,8 +6156,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="27254404" y="1180962"/>
-          <a:ext cx="1002500" cy="501650"/>
+          <a:off x="30150004" y="1180962"/>
+          <a:ext cx="1103465" cy="501650"/>
           <a:chOff x="1176" y="127"/>
           <a:chExt cx="136" cy="4"/>
         </a:xfrm>
@@ -6276,8 +6276,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="26404919" y="1209536"/>
-          <a:ext cx="737965" cy="511693"/>
+          <a:off x="29205269" y="1209536"/>
+          <a:ext cx="785590" cy="511693"/>
           <a:chOff x="1080" y="28"/>
           <a:chExt cx="76" cy="30"/>
         </a:xfrm>
@@ -6404,8 +6404,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="22526245" y="897593"/>
-          <a:ext cx="616889" cy="842963"/>
+          <a:off x="24945595" y="897593"/>
+          <a:ext cx="664514" cy="842963"/>
           <a:chOff x="286" y="112"/>
           <a:chExt cx="84" cy="59"/>
         </a:xfrm>
@@ -6524,8 +6524,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="28284489" y="912024"/>
-          <a:ext cx="626268" cy="1013614"/>
+          <a:off x="31275339" y="912024"/>
+          <a:ext cx="673893" cy="1013614"/>
           <a:chOff x="23788689" y="916786"/>
           <a:chExt cx="728662" cy="1013614"/>
         </a:xfrm>
@@ -15177,9 +15177,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -15217,7 +15217,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15323,7 +15323,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15465,7 +15465,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15477,21 +15477,21 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:V33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.21875" customWidth="1"/>
-    <col min="2" max="2" width="37.88671875" customWidth="1"/>
-    <col min="3" max="3" width="33.88671875" customWidth="1"/>
-    <col min="4" max="6" width="28.21875" customWidth="1"/>
-    <col min="7" max="17" width="5.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.19921875" customWidth="1"/>
+    <col min="2" max="2" width="37.8984375" customWidth="1"/>
+    <col min="3" max="3" width="33.8984375" customWidth="1"/>
+    <col min="4" max="6" width="28.19921875" customWidth="1"/>
+    <col min="7" max="17" width="5.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="25.8">
+    <row r="1" spans="1:22" ht="24.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="18">
+    <row r="2" spans="1:22" ht="17.399999999999999">
       <c r="B2" s="253" t="s">
         <v>1</v>
       </c>
@@ -16237,106 +16237,106 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A369FA75-54B8-4749-97B9-83AB9882043F}">
   <dimension ref="A1:K53"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" style="161" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" style="161" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="19" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="28.109375" style="19" customWidth="1"/>
-    <col min="5" max="5" width="3.6640625" style="176" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" style="19" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="161" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" style="176" customWidth="1"/>
-    <col min="9" max="9" width="39.44140625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="19" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="19"/>
+    <col min="3" max="3" width="3.69921875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="28.09765625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="3.69921875" style="176" customWidth="1"/>
+    <col min="6" max="6" width="30.09765625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="12.796875" style="161" customWidth="1"/>
+    <col min="8" max="8" width="3.69921875" style="176" customWidth="1"/>
+    <col min="9" max="9" width="39.3984375" style="19" customWidth="1"/>
+    <col min="10" max="10" width="18.09765625" style="19" customWidth="1"/>
+    <col min="11" max="11" width="39.3984375" style="19" customWidth="1"/>
+    <col min="12" max="16384" width="8.69921875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.4" thickBot="1">
-      <c r="A1" s="286" t="s">
+      <c r="A1" s="260" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="286"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="286"/>
-      <c r="E1" s="286"/>
-      <c r="F1" s="286"/>
-      <c r="G1" s="286"/>
-      <c r="H1" s="286"/>
-      <c r="I1" s="286"/>
-      <c r="J1" s="286"/>
-      <c r="K1" s="286"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
     </row>
     <row r="2" spans="1:11" ht="44.55" customHeight="1" thickBot="1">
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="261" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="288"/>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="289"/>
-      <c r="H2" s="290" t="s">
+      <c r="C2" s="262"/>
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="291"/>
-      <c r="J2" s="291"/>
-      <c r="K2" s="291"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
     </row>
     <row r="3" spans="1:11" s="20" customFormat="1" ht="21.6" customHeight="1">
-      <c r="A3" s="292" t="s">
+      <c r="A3" s="266" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="293" t="s">
+      <c r="B3" s="267" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="295" t="s">
+      <c r="C3" s="269" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="296"/>
-      <c r="E3" s="295" t="s">
+      <c r="D3" s="270"/>
+      <c r="E3" s="269" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="296"/>
-      <c r="G3" s="299" t="s">
+      <c r="F3" s="270"/>
+      <c r="G3" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="301" t="s">
+      <c r="H3" s="275" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="302"/>
-      <c r="J3" s="263" t="s">
+      <c r="I3" s="276"/>
+      <c r="J3" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="305" t="s">
+      <c r="K3" s="279" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="20" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A4" s="292"/>
-      <c r="B4" s="294"/>
-      <c r="C4" s="297"/>
-      <c r="D4" s="298"/>
-      <c r="E4" s="297"/>
-      <c r="F4" s="298"/>
-      <c r="G4" s="300"/>
-      <c r="H4" s="303"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="306"/>
+      <c r="A4" s="266"/>
+      <c r="B4" s="268"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="272"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="272"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="277"/>
+      <c r="I4" s="278"/>
+      <c r="J4" s="300"/>
+      <c r="K4" s="280"/>
     </row>
     <row r="5" spans="1:11" ht="31.2">
       <c r="A5" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="272" t="s">
+      <c r="B5" s="281" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="275">
+      <c r="C5" s="284">
         <v>1</v>
       </c>
-      <c r="D5" s="277" t="s">
+      <c r="D5" s="286" t="s">
         <v>208</v>
       </c>
       <c r="E5" s="163">
@@ -16363,9 +16363,9 @@
       <c r="A6" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="273"/>
-      <c r="C6" s="276"/>
-      <c r="D6" s="278"/>
+      <c r="B6" s="282"/>
+      <c r="C6" s="285"/>
+      <c r="D6" s="287"/>
       <c r="E6" s="21"/>
       <c r="F6" s="167"/>
       <c r="G6" s="168"/>
@@ -16378,11 +16378,11 @@
       <c r="A7" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="273"/>
-      <c r="C7" s="279">
+      <c r="B7" s="282"/>
+      <c r="C7" s="288">
         <v>2</v>
       </c>
-      <c r="D7" s="265" t="s">
+      <c r="D7" s="289" t="s">
         <v>209</v>
       </c>
       <c r="E7" s="21">
@@ -16403,15 +16403,15 @@
       <c r="J7" s="170" t="s">
         <v>297</v>
       </c>
-      <c r="K7" s="266" t="s">
+      <c r="K7" s="301" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="33" customHeight="1">
       <c r="A8" s="162"/>
-      <c r="B8" s="273"/>
-      <c r="C8" s="279"/>
-      <c r="D8" s="265"/>
+      <c r="B8" s="282"/>
+      <c r="C8" s="288"/>
+      <c r="D8" s="289"/>
       <c r="E8" s="21">
         <v>2</v>
       </c>
@@ -16430,13 +16430,13 @@
       <c r="J8" s="170" t="s">
         <v>298</v>
       </c>
-      <c r="K8" s="267"/>
+      <c r="K8" s="302"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="162"/>
-      <c r="B9" s="273"/>
-      <c r="C9" s="279"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="288"/>
+      <c r="D9" s="289"/>
       <c r="E9" s="21">
         <v>3</v>
       </c>
@@ -16453,13 +16453,13 @@
         <v>275</v>
       </c>
       <c r="J9" s="170"/>
-      <c r="K9" s="267"/>
+      <c r="K9" s="302"/>
     </row>
     <row r="10" spans="1:11" ht="29.4" customHeight="1">
       <c r="A10" s="162"/>
-      <c r="B10" s="273"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="265"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="288"/>
+      <c r="D10" s="289"/>
       <c r="E10" s="21">
         <v>4</v>
       </c>
@@ -16476,13 +16476,13 @@
         <v>276</v>
       </c>
       <c r="J10" s="170"/>
-      <c r="K10" s="267"/>
+      <c r="K10" s="302"/>
     </row>
     <row r="11" spans="1:11" ht="25.2" customHeight="1">
       <c r="A11" s="162"/>
-      <c r="B11" s="273"/>
-      <c r="C11" s="279"/>
-      <c r="D11" s="265"/>
+      <c r="B11" s="282"/>
+      <c r="C11" s="288"/>
+      <c r="D11" s="289"/>
       <c r="E11" s="21">
         <v>5</v>
       </c>
@@ -16499,15 +16499,15 @@
         <v>277</v>
       </c>
       <c r="J11" s="170"/>
-      <c r="K11" s="268"/>
+      <c r="K11" s="303"/>
     </row>
     <row r="12" spans="1:11" ht="25.2" customHeight="1">
       <c r="A12" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="273"/>
-      <c r="C12" s="279"/>
-      <c r="D12" s="265"/>
+      <c r="B12" s="282"/>
+      <c r="C12" s="288"/>
+      <c r="D12" s="289"/>
       <c r="E12" s="21">
         <v>6</v>
       </c>
@@ -16522,11 +16522,11 @@
       <c r="A13" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="273"/>
-      <c r="C13" s="280">
+      <c r="B13" s="282"/>
+      <c r="C13" s="290">
         <v>3</v>
       </c>
-      <c r="D13" s="265" t="s">
+      <c r="D13" s="289" t="s">
         <v>210</v>
       </c>
       <c r="E13" s="21">
@@ -16551,9 +16551,9 @@
     </row>
     <row r="14" spans="1:11" ht="39.6">
       <c r="A14" s="162"/>
-      <c r="B14" s="273"/>
-      <c r="C14" s="280"/>
-      <c r="D14" s="265"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="290"/>
+      <c r="D14" s="289"/>
       <c r="E14" s="21">
         <v>2</v>
       </c>
@@ -16576,9 +16576,9 @@
     </row>
     <row r="15" spans="1:11" ht="25.2" customHeight="1">
       <c r="A15" s="162"/>
-      <c r="B15" s="273"/>
-      <c r="C15" s="280"/>
-      <c r="D15" s="265"/>
+      <c r="B15" s="282"/>
+      <c r="C15" s="290"/>
+      <c r="D15" s="289"/>
       <c r="E15" s="21"/>
       <c r="F15" s="167"/>
       <c r="G15" s="168"/>
@@ -16591,11 +16591,11 @@
       <c r="A16" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B16" s="273"/>
-      <c r="C16" s="280">
+      <c r="B16" s="282"/>
+      <c r="C16" s="290">
         <v>5</v>
       </c>
-      <c r="D16" s="265" t="s">
+      <c r="D16" s="289" t="s">
         <v>211</v>
       </c>
       <c r="E16" s="21">
@@ -16622,9 +16622,9 @@
       <c r="A17" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B17" s="273"/>
-      <c r="C17" s="280"/>
-      <c r="D17" s="265"/>
+      <c r="B17" s="282"/>
+      <c r="C17" s="290"/>
+      <c r="D17" s="289"/>
       <c r="E17" s="21"/>
       <c r="F17" s="167"/>
       <c r="G17" s="168"/>
@@ -16641,9 +16641,9 @@
     </row>
     <row r="18" spans="1:11" ht="25.2" customHeight="1">
       <c r="A18" s="162"/>
-      <c r="B18" s="273"/>
-      <c r="C18" s="280"/>
-      <c r="D18" s="265"/>
+      <c r="B18" s="282"/>
+      <c r="C18" s="290"/>
+      <c r="D18" s="289"/>
       <c r="E18" s="21"/>
       <c r="F18" s="167"/>
       <c r="G18" s="168"/>
@@ -16656,11 +16656,11 @@
       <c r="A19" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="273"/>
-      <c r="C19" s="280">
+      <c r="B19" s="282"/>
+      <c r="C19" s="290">
         <v>6</v>
       </c>
-      <c r="D19" s="265" t="s">
+      <c r="D19" s="289" t="s">
         <v>212</v>
       </c>
       <c r="E19" s="21">
@@ -16679,9 +16679,9 @@
     </row>
     <row r="20" spans="1:11" ht="29.4" customHeight="1">
       <c r="A20" s="162"/>
-      <c r="B20" s="273"/>
-      <c r="C20" s="280"/>
-      <c r="D20" s="265"/>
+      <c r="B20" s="282"/>
+      <c r="C20" s="290"/>
+      <c r="D20" s="289"/>
       <c r="E20" s="21"/>
       <c r="F20" s="167" t="s">
         <v>239</v>
@@ -16700,9 +16700,9 @@
     </row>
     <row r="21" spans="1:11" ht="29.4" customHeight="1">
       <c r="A21" s="162"/>
-      <c r="B21" s="273"/>
-      <c r="C21" s="280"/>
-      <c r="D21" s="265"/>
+      <c r="B21" s="282"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="289"/>
       <c r="E21" s="21"/>
       <c r="F21" s="167"/>
       <c r="G21" s="168"/>
@@ -16719,9 +16719,9 @@
     </row>
     <row r="22" spans="1:11" ht="72.599999999999994" customHeight="1">
       <c r="A22" s="162"/>
-      <c r="B22" s="273"/>
-      <c r="C22" s="280"/>
-      <c r="D22" s="265"/>
+      <c r="B22" s="282"/>
+      <c r="C22" s="290"/>
+      <c r="D22" s="289"/>
       <c r="E22" s="21"/>
       <c r="F22" s="167"/>
       <c r="G22" s="168"/>
@@ -16738,9 +16738,9 @@
     </row>
     <row r="23" spans="1:11" ht="29.4" customHeight="1">
       <c r="A23" s="162"/>
-      <c r="B23" s="273"/>
-      <c r="C23" s="280"/>
-      <c r="D23" s="265"/>
+      <c r="B23" s="282"/>
+      <c r="C23" s="290"/>
+      <c r="D23" s="289"/>
       <c r="E23" s="21">
         <v>2</v>
       </c>
@@ -16761,9 +16761,9 @@
     </row>
     <row r="24" spans="1:11" ht="29.4" customHeight="1">
       <c r="A24" s="162"/>
-      <c r="B24" s="273"/>
-      <c r="C24" s="280"/>
-      <c r="D24" s="265"/>
+      <c r="B24" s="282"/>
+      <c r="C24" s="290"/>
+      <c r="D24" s="289"/>
       <c r="E24" s="21"/>
       <c r="F24" s="167"/>
       <c r="G24" s="168"/>
@@ -16780,9 +16780,9 @@
     </row>
     <row r="25" spans="1:11" ht="31.2">
       <c r="A25" s="162"/>
-      <c r="B25" s="273"/>
-      <c r="C25" s="280"/>
-      <c r="D25" s="265"/>
+      <c r="B25" s="282"/>
+      <c r="C25" s="290"/>
+      <c r="D25" s="289"/>
       <c r="E25" s="21"/>
       <c r="F25" s="167"/>
       <c r="G25" s="168"/>
@@ -16799,9 +16799,9 @@
     </row>
     <row r="26" spans="1:11" ht="25.2" customHeight="1">
       <c r="A26" s="162"/>
-      <c r="B26" s="273"/>
-      <c r="C26" s="280"/>
-      <c r="D26" s="265"/>
+      <c r="B26" s="282"/>
+      <c r="C26" s="290"/>
+      <c r="D26" s="289"/>
       <c r="E26" s="21">
         <v>3</v>
       </c>
@@ -16820,9 +16820,9 @@
     </row>
     <row r="27" spans="1:11" ht="25.2" customHeight="1">
       <c r="A27" s="162"/>
-      <c r="B27" s="273"/>
-      <c r="C27" s="280"/>
-      <c r="D27" s="265"/>
+      <c r="B27" s="282"/>
+      <c r="C27" s="290"/>
+      <c r="D27" s="289"/>
       <c r="E27" s="21"/>
       <c r="F27" s="167"/>
       <c r="G27" s="168"/>
@@ -16831,15 +16831,15 @@
         <v>222</v>
       </c>
       <c r="J27" s="170"/>
-      <c r="K27" s="269" t="s">
+      <c r="K27" s="304" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.2" customHeight="1">
       <c r="A28" s="162"/>
-      <c r="B28" s="273"/>
-      <c r="C28" s="280"/>
-      <c r="D28" s="265"/>
+      <c r="B28" s="282"/>
+      <c r="C28" s="290"/>
+      <c r="D28" s="289"/>
       <c r="E28" s="21"/>
       <c r="F28" s="167"/>
       <c r="G28" s="168"/>
@@ -16848,13 +16848,13 @@
         <v>223</v>
       </c>
       <c r="J28" s="170"/>
-      <c r="K28" s="270"/>
+      <c r="K28" s="305"/>
     </row>
     <row r="29" spans="1:11" ht="25.2" customHeight="1">
       <c r="A29" s="162"/>
-      <c r="B29" s="273"/>
-      <c r="C29" s="280"/>
-      <c r="D29" s="265"/>
+      <c r="B29" s="282"/>
+      <c r="C29" s="290"/>
+      <c r="D29" s="289"/>
       <c r="E29" s="21"/>
       <c r="F29" s="167"/>
       <c r="G29" s="168"/>
@@ -16863,13 +16863,13 @@
         <v>224</v>
       </c>
       <c r="J29" s="170"/>
-      <c r="K29" s="271"/>
+      <c r="K29" s="306"/>
     </row>
     <row r="30" spans="1:11" ht="25.2" customHeight="1">
       <c r="A30" s="162"/>
-      <c r="B30" s="273"/>
-      <c r="C30" s="280"/>
-      <c r="D30" s="265"/>
+      <c r="B30" s="282"/>
+      <c r="C30" s="290"/>
+      <c r="D30" s="289"/>
       <c r="E30" s="21">
         <v>4</v>
       </c>
@@ -16888,9 +16888,9 @@
     </row>
     <row r="31" spans="1:11" ht="25.2" customHeight="1">
       <c r="A31" s="162"/>
-      <c r="B31" s="273"/>
-      <c r="C31" s="280"/>
-      <c r="D31" s="265"/>
+      <c r="B31" s="282"/>
+      <c r="C31" s="290"/>
+      <c r="D31" s="289"/>
       <c r="E31" s="21"/>
       <c r="F31" s="167"/>
       <c r="G31" s="168"/>
@@ -16905,9 +16905,9 @@
     </row>
     <row r="32" spans="1:11" ht="25.2" customHeight="1">
       <c r="A32" s="162"/>
-      <c r="B32" s="273"/>
-      <c r="C32" s="280"/>
-      <c r="D32" s="265"/>
+      <c r="B32" s="282"/>
+      <c r="C32" s="290"/>
+      <c r="D32" s="289"/>
       <c r="E32" s="21"/>
       <c r="F32" s="167"/>
       <c r="G32" s="168"/>
@@ -16916,15 +16916,15 @@
         <v>227</v>
       </c>
       <c r="J32" s="170"/>
-      <c r="K32" s="269" t="s">
+      <c r="K32" s="304" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.2" customHeight="1">
       <c r="A33" s="162"/>
-      <c r="B33" s="273"/>
-      <c r="C33" s="280"/>
-      <c r="D33" s="265"/>
+      <c r="B33" s="282"/>
+      <c r="C33" s="290"/>
+      <c r="D33" s="289"/>
       <c r="E33" s="21"/>
       <c r="F33" s="167"/>
       <c r="G33" s="168"/>
@@ -16933,13 +16933,13 @@
         <v>229</v>
       </c>
       <c r="J33" s="170"/>
-      <c r="K33" s="270"/>
+      <c r="K33" s="305"/>
     </row>
     <row r="34" spans="1:11" ht="25.2" customHeight="1">
       <c r="A34" s="162"/>
-      <c r="B34" s="273"/>
-      <c r="C34" s="280"/>
-      <c r="D34" s="265"/>
+      <c r="B34" s="282"/>
+      <c r="C34" s="290"/>
+      <c r="D34" s="289"/>
       <c r="E34" s="21"/>
       <c r="F34" s="167"/>
       <c r="G34" s="168"/>
@@ -16948,13 +16948,13 @@
         <v>228</v>
       </c>
       <c r="J34" s="170"/>
-      <c r="K34" s="271"/>
+      <c r="K34" s="306"/>
     </row>
     <row r="35" spans="1:11" ht="31.8" customHeight="1">
       <c r="A35" s="162"/>
-      <c r="B35" s="273"/>
-      <c r="C35" s="280"/>
-      <c r="D35" s="265"/>
+      <c r="B35" s="282"/>
+      <c r="C35" s="290"/>
+      <c r="D35" s="289"/>
       <c r="E35" s="21">
         <v>5</v>
       </c>
@@ -16975,11 +16975,11 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="31.2">
+    <row r="36" spans="1:11" ht="19.8">
       <c r="A36" s="162"/>
-      <c r="B36" s="273"/>
-      <c r="C36" s="280"/>
-      <c r="D36" s="265"/>
+      <c r="B36" s="282"/>
+      <c r="C36" s="290"/>
+      <c r="D36" s="289"/>
       <c r="E36" s="21"/>
       <c r="F36" s="167"/>
       <c r="G36" s="168"/>
@@ -16996,9 +16996,9 @@
     </row>
     <row r="37" spans="1:11" ht="25.2" customHeight="1">
       <c r="A37" s="162"/>
-      <c r="B37" s="273"/>
-      <c r="C37" s="280"/>
-      <c r="D37" s="265"/>
+      <c r="B37" s="282"/>
+      <c r="C37" s="290"/>
+      <c r="D37" s="289"/>
       <c r="E37" s="21">
         <v>6</v>
       </c>
@@ -17017,9 +17017,9 @@
     </row>
     <row r="38" spans="1:11" ht="25.2" customHeight="1">
       <c r="A38" s="162"/>
-      <c r="B38" s="273"/>
-      <c r="C38" s="280"/>
-      <c r="D38" s="265"/>
+      <c r="B38" s="282"/>
+      <c r="C38" s="290"/>
+      <c r="D38" s="289"/>
       <c r="E38" s="21"/>
       <c r="F38" s="167"/>
       <c r="G38" s="168"/>
@@ -17034,9 +17034,9 @@
     </row>
     <row r="39" spans="1:11" ht="25.2" customHeight="1">
       <c r="A39" s="162"/>
-      <c r="B39" s="273"/>
-      <c r="C39" s="280"/>
-      <c r="D39" s="265"/>
+      <c r="B39" s="282"/>
+      <c r="C39" s="290"/>
+      <c r="D39" s="289"/>
       <c r="E39" s="21"/>
       <c r="F39" s="167"/>
       <c r="G39" s="168"/>
@@ -17051,9 +17051,9 @@
     </row>
     <row r="40" spans="1:11" ht="76.8" customHeight="1">
       <c r="A40" s="162"/>
-      <c r="B40" s="273"/>
-      <c r="C40" s="280"/>
-      <c r="D40" s="265"/>
+      <c r="B40" s="282"/>
+      <c r="C40" s="290"/>
+      <c r="D40" s="289"/>
       <c r="E40" s="21">
         <v>7</v>
       </c>
@@ -17076,11 +17076,11 @@
     </row>
     <row r="41" spans="1:11" ht="39.6">
       <c r="A41" s="162"/>
-      <c r="B41" s="273"/>
-      <c r="C41" s="280">
+      <c r="B41" s="282"/>
+      <c r="C41" s="290">
         <v>7</v>
       </c>
-      <c r="D41" s="265" t="s">
+      <c r="D41" s="289" t="s">
         <v>213</v>
       </c>
       <c r="E41" s="21">
@@ -17105,9 +17105,9 @@
     </row>
     <row r="42" spans="1:11" ht="19.8">
       <c r="A42" s="162"/>
-      <c r="B42" s="273"/>
-      <c r="C42" s="280"/>
-      <c r="D42" s="265"/>
+      <c r="B42" s="282"/>
+      <c r="C42" s="290"/>
+      <c r="D42" s="289"/>
       <c r="E42" s="21"/>
       <c r="F42" s="167"/>
       <c r="G42" s="168"/>
@@ -17118,15 +17118,15 @@
         <v>245</v>
       </c>
       <c r="J42" s="170"/>
-      <c r="K42" s="260" t="s">
+      <c r="K42" s="296" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="31.2">
       <c r="A43" s="162"/>
-      <c r="B43" s="273"/>
-      <c r="C43" s="280"/>
-      <c r="D43" s="265"/>
+      <c r="B43" s="282"/>
+      <c r="C43" s="290"/>
+      <c r="D43" s="289"/>
       <c r="E43" s="21"/>
       <c r="F43" s="167"/>
       <c r="G43" s="168"/>
@@ -17137,13 +17137,13 @@
         <v>246</v>
       </c>
       <c r="J43" s="170"/>
-      <c r="K43" s="262"/>
+      <c r="K43" s="298"/>
     </row>
     <row r="44" spans="1:11" ht="25.2" customHeight="1">
       <c r="A44" s="162"/>
-      <c r="B44" s="273"/>
-      <c r="C44" s="280"/>
-      <c r="D44" s="265"/>
+      <c r="B44" s="282"/>
+      <c r="C44" s="290"/>
+      <c r="D44" s="289"/>
       <c r="E44" s="21">
         <v>2</v>
       </c>
@@ -17166,9 +17166,9 @@
     </row>
     <row r="45" spans="1:11" ht="25.2" customHeight="1">
       <c r="A45" s="162"/>
-      <c r="B45" s="273"/>
-      <c r="C45" s="280"/>
-      <c r="D45" s="265"/>
+      <c r="B45" s="282"/>
+      <c r="C45" s="290"/>
+      <c r="D45" s="289"/>
       <c r="E45" s="21"/>
       <c r="F45" s="167"/>
       <c r="G45" s="168"/>
@@ -17179,11 +17179,11 @@
     </row>
     <row r="46" spans="1:11" ht="39.6">
       <c r="A46" s="162"/>
-      <c r="B46" s="273"/>
-      <c r="C46" s="280">
+      <c r="B46" s="282"/>
+      <c r="C46" s="290">
         <v>8</v>
       </c>
-      <c r="D46" s="265" t="s">
+      <c r="D46" s="289" t="s">
         <v>214</v>
       </c>
       <c r="E46" s="21">
@@ -17208,9 +17208,9 @@
     </row>
     <row r="47" spans="1:11" ht="25.2" customHeight="1">
       <c r="A47" s="162"/>
-      <c r="B47" s="273"/>
-      <c r="C47" s="280"/>
-      <c r="D47" s="265"/>
+      <c r="B47" s="282"/>
+      <c r="C47" s="290"/>
+      <c r="D47" s="289"/>
       <c r="E47" s="21"/>
       <c r="F47" s="167"/>
       <c r="G47" s="168"/>
@@ -17221,11 +17221,11 @@
     </row>
     <row r="48" spans="1:11" ht="25.2" customHeight="1">
       <c r="A48" s="162"/>
-      <c r="B48" s="273"/>
-      <c r="C48" s="284">
+      <c r="B48" s="282"/>
+      <c r="C48" s="294">
         <v>9</v>
       </c>
-      <c r="D48" s="281" t="s">
+      <c r="D48" s="291" t="s">
         <v>215</v>
       </c>
       <c r="E48" s="183">
@@ -17248,9 +17248,9 @@
     </row>
     <row r="49" spans="1:11" ht="25.2" customHeight="1">
       <c r="A49" s="162"/>
-      <c r="B49" s="273"/>
-      <c r="C49" s="275"/>
-      <c r="D49" s="282"/>
+      <c r="B49" s="282"/>
+      <c r="C49" s="284"/>
+      <c r="D49" s="292"/>
       <c r="E49" s="183"/>
       <c r="F49" s="22"/>
       <c r="G49" s="182"/>
@@ -17261,15 +17261,15 @@
       <c r="J49" s="170" t="s">
         <v>264</v>
       </c>
-      <c r="K49" s="260" t="s">
+      <c r="K49" s="296" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="25.2" customHeight="1">
       <c r="A50" s="162"/>
-      <c r="B50" s="273"/>
-      <c r="C50" s="275"/>
-      <c r="D50" s="282"/>
+      <c r="B50" s="282"/>
+      <c r="C50" s="284"/>
+      <c r="D50" s="292"/>
       <c r="E50" s="183"/>
       <c r="F50" s="22"/>
       <c r="G50" s="182"/>
@@ -17280,13 +17280,13 @@
       <c r="J50" s="170" t="s">
         <v>265</v>
       </c>
-      <c r="K50" s="261"/>
+      <c r="K50" s="297"/>
     </row>
     <row r="51" spans="1:11" ht="25.2" customHeight="1">
       <c r="A51" s="162"/>
-      <c r="B51" s="273"/>
-      <c r="C51" s="275"/>
-      <c r="D51" s="282"/>
+      <c r="B51" s="282"/>
+      <c r="C51" s="284"/>
+      <c r="D51" s="292"/>
       <c r="E51" s="183"/>
       <c r="F51" s="22"/>
       <c r="G51" s="182"/>
@@ -17297,13 +17297,13 @@
       <c r="J51" s="170" t="s">
         <v>266</v>
       </c>
-      <c r="K51" s="261"/>
+      <c r="K51" s="297"/>
     </row>
     <row r="52" spans="1:11" ht="31.2" customHeight="1">
       <c r="A52" s="162"/>
-      <c r="B52" s="273"/>
-      <c r="C52" s="275"/>
-      <c r="D52" s="282"/>
+      <c r="B52" s="282"/>
+      <c r="C52" s="284"/>
+      <c r="D52" s="292"/>
       <c r="E52" s="21"/>
       <c r="F52" s="167"/>
       <c r="G52" s="168"/>
@@ -17314,13 +17314,13 @@
       <c r="J52" s="187" t="s">
         <v>301</v>
       </c>
-      <c r="K52" s="262"/>
+      <c r="K52" s="298"/>
     </row>
     <row r="53" spans="1:11" ht="24" customHeight="1" thickBot="1">
       <c r="A53" s="162"/>
-      <c r="B53" s="274"/>
-      <c r="C53" s="285"/>
-      <c r="D53" s="283"/>
+      <c r="B53" s="283"/>
+      <c r="C53" s="295"/>
+      <c r="D53" s="293"/>
       <c r="E53" s="171"/>
       <c r="F53" s="172"/>
       <c r="G53" s="173"/>
@@ -17333,16 +17333,13 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:I4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K49:K52"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="K7:K11"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="K32:K34"/>
+    <mergeCell ref="K42:K43"/>
     <mergeCell ref="B5:B53"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -17359,13 +17356,16 @@
     <mergeCell ref="C41:C45"/>
     <mergeCell ref="D41:D45"/>
     <mergeCell ref="C46:C47"/>
-    <mergeCell ref="K49:K52"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="K7:K11"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="K32:K34"/>
-    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="K3:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17375,106 +17375,106 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC59FD44-57D8-4CAD-B8FF-B0C420BF9226}">
   <dimension ref="A1:K55"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" style="161" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" style="161" customWidth="1"/>
     <col min="2" max="2" width="18" style="19" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="29.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="3.6640625" style="176" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" style="19" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="161" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" style="176" customWidth="1"/>
-    <col min="9" max="9" width="39.44140625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="19" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="19"/>
+    <col min="3" max="3" width="3.69921875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="29.3984375" style="19" customWidth="1"/>
+    <col min="5" max="5" width="3.69921875" style="176" customWidth="1"/>
+    <col min="6" max="6" width="30.09765625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="12.796875" style="161" customWidth="1"/>
+    <col min="8" max="8" width="3.69921875" style="176" customWidth="1"/>
+    <col min="9" max="9" width="39.3984375" style="19" customWidth="1"/>
+    <col min="10" max="10" width="18.09765625" style="19" customWidth="1"/>
+    <col min="11" max="11" width="39.3984375" style="19" customWidth="1"/>
+    <col min="12" max="16384" width="8.69921875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.4" thickBot="1">
-      <c r="A1" s="286" t="s">
+      <c r="A1" s="260" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="286"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="286"/>
-      <c r="E1" s="286"/>
-      <c r="F1" s="286"/>
-      <c r="G1" s="286"/>
-      <c r="H1" s="286"/>
-      <c r="I1" s="286"/>
-      <c r="J1" s="286"/>
-      <c r="K1" s="286"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
     </row>
     <row r="2" spans="1:11" ht="44.55" customHeight="1" thickBot="1">
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="261" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="288"/>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="289"/>
-      <c r="H2" s="290" t="s">
+      <c r="C2" s="262"/>
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="291"/>
-      <c r="J2" s="291"/>
-      <c r="K2" s="291"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
     </row>
     <row r="3" spans="1:11" s="20" customFormat="1" ht="21.6" customHeight="1">
-      <c r="A3" s="292" t="s">
+      <c r="A3" s="266" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="293" t="s">
+      <c r="B3" s="267" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="295" t="s">
+      <c r="C3" s="269" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="296"/>
-      <c r="E3" s="295" t="s">
+      <c r="D3" s="270"/>
+      <c r="E3" s="269" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="296"/>
-      <c r="G3" s="299" t="s">
+      <c r="F3" s="270"/>
+      <c r="G3" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="301" t="s">
+      <c r="H3" s="275" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="302"/>
-      <c r="J3" s="263" t="s">
+      <c r="I3" s="276"/>
+      <c r="J3" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="305" t="s">
+      <c r="K3" s="279" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="20" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A4" s="292"/>
-      <c r="B4" s="294"/>
-      <c r="C4" s="297"/>
-      <c r="D4" s="298"/>
-      <c r="E4" s="297"/>
-      <c r="F4" s="298"/>
-      <c r="G4" s="300"/>
-      <c r="H4" s="303"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="306"/>
+      <c r="A4" s="266"/>
+      <c r="B4" s="268"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="272"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="272"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="277"/>
+      <c r="I4" s="278"/>
+      <c r="J4" s="300"/>
+      <c r="K4" s="280"/>
     </row>
     <row r="5" spans="1:11" ht="31.2">
       <c r="A5" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="272" t="s">
+      <c r="B5" s="281" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="275">
+      <c r="C5" s="284">
         <v>1</v>
       </c>
-      <c r="D5" s="277" t="s">
+      <c r="D5" s="286" t="s">
         <v>208</v>
       </c>
       <c r="E5" s="163">
@@ -17501,9 +17501,9 @@
       <c r="A6" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="273"/>
-      <c r="C6" s="276"/>
-      <c r="D6" s="278"/>
+      <c r="B6" s="282"/>
+      <c r="C6" s="285"/>
+      <c r="D6" s="287"/>
       <c r="E6" s="21"/>
       <c r="F6" s="167"/>
       <c r="G6" s="168"/>
@@ -17516,11 +17516,11 @@
       <c r="A7" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="273"/>
-      <c r="C7" s="279">
+      <c r="B7" s="282"/>
+      <c r="C7" s="288">
         <v>2</v>
       </c>
-      <c r="D7" s="265" t="s">
+      <c r="D7" s="289" t="s">
         <v>303</v>
       </c>
       <c r="E7" s="21">
@@ -17547,9 +17547,9 @@
     </row>
     <row r="8" spans="1:11" ht="33" customHeight="1">
       <c r="A8" s="162"/>
-      <c r="B8" s="273"/>
-      <c r="C8" s="279"/>
-      <c r="D8" s="265"/>
+      <c r="B8" s="282"/>
+      <c r="C8" s="288"/>
+      <c r="D8" s="289"/>
       <c r="E8" s="21">
         <v>2</v>
       </c>
@@ -17572,9 +17572,9 @@
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="162"/>
-      <c r="B9" s="273"/>
-      <c r="C9" s="279"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="288"/>
+      <c r="D9" s="289"/>
       <c r="E9" s="21">
         <v>3</v>
       </c>
@@ -17595,9 +17595,9 @@
     </row>
     <row r="10" spans="1:11" ht="29.4" customHeight="1">
       <c r="A10" s="162"/>
-      <c r="B10" s="273"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="265"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="288"/>
+      <c r="D10" s="289"/>
       <c r="E10" s="21">
         <v>4</v>
       </c>
@@ -17618,9 +17618,9 @@
     </row>
     <row r="11" spans="1:11" ht="25.2" customHeight="1">
       <c r="A11" s="162"/>
-      <c r="B11" s="273"/>
-      <c r="C11" s="279"/>
-      <c r="D11" s="265"/>
+      <c r="B11" s="282"/>
+      <c r="C11" s="288"/>
+      <c r="D11" s="289"/>
       <c r="E11" s="21">
         <v>5</v>
       </c>
@@ -17643,9 +17643,9 @@
       <c r="A12" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="273"/>
-      <c r="C12" s="279"/>
-      <c r="D12" s="265"/>
+      <c r="B12" s="282"/>
+      <c r="C12" s="288"/>
+      <c r="D12" s="289"/>
       <c r="E12" s="21">
         <v>6</v>
       </c>
@@ -17660,11 +17660,11 @@
       <c r="A13" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="273"/>
-      <c r="C13" s="280">
+      <c r="B13" s="282"/>
+      <c r="C13" s="290">
         <v>9</v>
       </c>
-      <c r="D13" s="265" t="s">
+      <c r="D13" s="289" t="s">
         <v>210</v>
       </c>
       <c r="E13" s="21">
@@ -17689,9 +17689,9 @@
     </row>
     <row r="14" spans="1:11" ht="39.6">
       <c r="A14" s="162"/>
-      <c r="B14" s="273"/>
-      <c r="C14" s="280"/>
-      <c r="D14" s="265"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="290"/>
+      <c r="D14" s="289"/>
       <c r="E14" s="21">
         <v>2</v>
       </c>
@@ -17714,9 +17714,9 @@
     </row>
     <row r="15" spans="1:11" ht="25.2" customHeight="1">
       <c r="A15" s="162"/>
-      <c r="B15" s="273"/>
-      <c r="C15" s="280"/>
-      <c r="D15" s="265"/>
+      <c r="B15" s="282"/>
+      <c r="C15" s="290"/>
+      <c r="D15" s="289"/>
       <c r="E15" s="21"/>
       <c r="F15" s="167"/>
       <c r="G15" s="168"/>
@@ -17729,11 +17729,11 @@
       <c r="A16" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B16" s="273"/>
-      <c r="C16" s="280">
+      <c r="B16" s="282"/>
+      <c r="C16" s="290">
         <v>10</v>
       </c>
-      <c r="D16" s="265" t="s">
+      <c r="D16" s="289" t="s">
         <v>211</v>
       </c>
       <c r="E16" s="21">
@@ -17760,9 +17760,9 @@
       <c r="A17" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B17" s="273"/>
-      <c r="C17" s="280"/>
-      <c r="D17" s="265"/>
+      <c r="B17" s="282"/>
+      <c r="C17" s="290"/>
+      <c r="D17" s="289"/>
       <c r="E17" s="21"/>
       <c r="F17" s="167"/>
       <c r="G17" s="168"/>
@@ -17779,9 +17779,9 @@
     </row>
     <row r="18" spans="1:11" ht="25.2" customHeight="1">
       <c r="A18" s="162"/>
-      <c r="B18" s="273"/>
-      <c r="C18" s="280"/>
-      <c r="D18" s="265"/>
+      <c r="B18" s="282"/>
+      <c r="C18" s="290"/>
+      <c r="D18" s="289"/>
       <c r="E18" s="21"/>
       <c r="F18" s="167"/>
       <c r="G18" s="168"/>
@@ -17794,11 +17794,11 @@
       <c r="A19" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="273"/>
-      <c r="C19" s="280">
+      <c r="B19" s="282"/>
+      <c r="C19" s="290">
         <v>11</v>
       </c>
-      <c r="D19" s="265" t="s">
+      <c r="D19" s="289" t="s">
         <v>212</v>
       </c>
       <c r="E19" s="21">
@@ -17817,9 +17817,9 @@
     </row>
     <row r="20" spans="1:11" ht="29.4" customHeight="1">
       <c r="A20" s="162"/>
-      <c r="B20" s="273"/>
-      <c r="C20" s="280"/>
-      <c r="D20" s="265"/>
+      <c r="B20" s="282"/>
+      <c r="C20" s="290"/>
+      <c r="D20" s="289"/>
       <c r="E20" s="21"/>
       <c r="F20" s="167" t="s">
         <v>239</v>
@@ -17838,9 +17838,9 @@
     </row>
     <row r="21" spans="1:11" ht="29.4" customHeight="1">
       <c r="A21" s="162"/>
-      <c r="B21" s="273"/>
-      <c r="C21" s="280"/>
-      <c r="D21" s="265"/>
+      <c r="B21" s="282"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="289"/>
       <c r="E21" s="21"/>
       <c r="F21" s="167"/>
       <c r="G21" s="168"/>
@@ -17857,9 +17857,9 @@
     </row>
     <row r="22" spans="1:11" ht="72.599999999999994" customHeight="1">
       <c r="A22" s="162"/>
-      <c r="B22" s="273"/>
-      <c r="C22" s="280"/>
-      <c r="D22" s="265"/>
+      <c r="B22" s="282"/>
+      <c r="C22" s="290"/>
+      <c r="D22" s="289"/>
       <c r="E22" s="21"/>
       <c r="F22" s="167"/>
       <c r="G22" s="168"/>
@@ -17876,9 +17876,9 @@
     </row>
     <row r="23" spans="1:11" ht="29.4" customHeight="1">
       <c r="A23" s="162"/>
-      <c r="B23" s="273"/>
-      <c r="C23" s="280"/>
-      <c r="D23" s="265"/>
+      <c r="B23" s="282"/>
+      <c r="C23" s="290"/>
+      <c r="D23" s="289"/>
       <c r="E23" s="21">
         <v>2</v>
       </c>
@@ -17899,9 +17899,9 @@
     </row>
     <row r="24" spans="1:11" ht="29.4" customHeight="1">
       <c r="A24" s="162"/>
-      <c r="B24" s="273"/>
-      <c r="C24" s="280"/>
-      <c r="D24" s="265"/>
+      <c r="B24" s="282"/>
+      <c r="C24" s="290"/>
+      <c r="D24" s="289"/>
       <c r="E24" s="21"/>
       <c r="F24" s="167"/>
       <c r="G24" s="168"/>
@@ -17918,9 +17918,9 @@
     </row>
     <row r="25" spans="1:11" ht="31.2">
       <c r="A25" s="162"/>
-      <c r="B25" s="273"/>
-      <c r="C25" s="280"/>
-      <c r="D25" s="265"/>
+      <c r="B25" s="282"/>
+      <c r="C25" s="290"/>
+      <c r="D25" s="289"/>
       <c r="E25" s="21"/>
       <c r="F25" s="167"/>
       <c r="G25" s="168"/>
@@ -17937,9 +17937,9 @@
     </row>
     <row r="26" spans="1:11" ht="25.2" customHeight="1">
       <c r="A26" s="162"/>
-      <c r="B26" s="273"/>
-      <c r="C26" s="280"/>
-      <c r="D26" s="265"/>
+      <c r="B26" s="282"/>
+      <c r="C26" s="290"/>
+      <c r="D26" s="289"/>
       <c r="E26" s="21">
         <v>3</v>
       </c>
@@ -17958,9 +17958,9 @@
     </row>
     <row r="27" spans="1:11" ht="25.2" customHeight="1">
       <c r="A27" s="162"/>
-      <c r="B27" s="273"/>
-      <c r="C27" s="280"/>
-      <c r="D27" s="265"/>
+      <c r="B27" s="282"/>
+      <c r="C27" s="290"/>
+      <c r="D27" s="289"/>
       <c r="E27" s="21"/>
       <c r="F27" s="167"/>
       <c r="G27" s="168"/>
@@ -17969,15 +17969,15 @@
         <v>222</v>
       </c>
       <c r="J27" s="170"/>
-      <c r="K27" s="269" t="s">
+      <c r="K27" s="304" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.2" customHeight="1">
       <c r="A28" s="162"/>
-      <c r="B28" s="273"/>
-      <c r="C28" s="280"/>
-      <c r="D28" s="265"/>
+      <c r="B28" s="282"/>
+      <c r="C28" s="290"/>
+      <c r="D28" s="289"/>
       <c r="E28" s="21"/>
       <c r="F28" s="167"/>
       <c r="G28" s="168"/>
@@ -17986,13 +17986,13 @@
         <v>223</v>
       </c>
       <c r="J28" s="170"/>
-      <c r="K28" s="270"/>
+      <c r="K28" s="305"/>
     </row>
     <row r="29" spans="1:11" ht="25.2" customHeight="1">
       <c r="A29" s="162"/>
-      <c r="B29" s="273"/>
-      <c r="C29" s="280"/>
-      <c r="D29" s="265"/>
+      <c r="B29" s="282"/>
+      <c r="C29" s="290"/>
+      <c r="D29" s="289"/>
       <c r="E29" s="21"/>
       <c r="F29" s="167"/>
       <c r="G29" s="168"/>
@@ -18001,13 +18001,13 @@
         <v>224</v>
       </c>
       <c r="J29" s="170"/>
-      <c r="K29" s="271"/>
+      <c r="K29" s="306"/>
     </row>
     <row r="30" spans="1:11" ht="25.2" customHeight="1">
       <c r="A30" s="162"/>
-      <c r="B30" s="273"/>
-      <c r="C30" s="280"/>
-      <c r="D30" s="265"/>
+      <c r="B30" s="282"/>
+      <c r="C30" s="290"/>
+      <c r="D30" s="289"/>
       <c r="E30" s="21">
         <v>4</v>
       </c>
@@ -18026,9 +18026,9 @@
     </row>
     <row r="31" spans="1:11" ht="25.2" customHeight="1">
       <c r="A31" s="162"/>
-      <c r="B31" s="273"/>
-      <c r="C31" s="280"/>
-      <c r="D31" s="265"/>
+      <c r="B31" s="282"/>
+      <c r="C31" s="290"/>
+      <c r="D31" s="289"/>
       <c r="E31" s="21"/>
       <c r="F31" s="167"/>
       <c r="G31" s="168"/>
@@ -18043,9 +18043,9 @@
     </row>
     <row r="32" spans="1:11" ht="25.2" customHeight="1">
       <c r="A32" s="162"/>
-      <c r="B32" s="273"/>
-      <c r="C32" s="280"/>
-      <c r="D32" s="265"/>
+      <c r="B32" s="282"/>
+      <c r="C32" s="290"/>
+      <c r="D32" s="289"/>
       <c r="E32" s="21"/>
       <c r="F32" s="167"/>
       <c r="G32" s="168"/>
@@ -18054,15 +18054,15 @@
         <v>227</v>
       </c>
       <c r="J32" s="170"/>
-      <c r="K32" s="269" t="s">
+      <c r="K32" s="304" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.2" customHeight="1">
       <c r="A33" s="162"/>
-      <c r="B33" s="273"/>
-      <c r="C33" s="280"/>
-      <c r="D33" s="265"/>
+      <c r="B33" s="282"/>
+      <c r="C33" s="290"/>
+      <c r="D33" s="289"/>
       <c r="E33" s="21"/>
       <c r="F33" s="167"/>
       <c r="G33" s="168"/>
@@ -18071,13 +18071,13 @@
         <v>229</v>
       </c>
       <c r="J33" s="170"/>
-      <c r="K33" s="270"/>
+      <c r="K33" s="305"/>
     </row>
     <row r="34" spans="1:11" ht="25.2" customHeight="1">
       <c r="A34" s="162"/>
-      <c r="B34" s="273"/>
-      <c r="C34" s="280"/>
-      <c r="D34" s="265"/>
+      <c r="B34" s="282"/>
+      <c r="C34" s="290"/>
+      <c r="D34" s="289"/>
       <c r="E34" s="21"/>
       <c r="F34" s="167"/>
       <c r="G34" s="168"/>
@@ -18086,13 +18086,13 @@
         <v>228</v>
       </c>
       <c r="J34" s="170"/>
-      <c r="K34" s="271"/>
+      <c r="K34" s="306"/>
     </row>
     <row r="35" spans="1:11" ht="31.8" customHeight="1">
       <c r="A35" s="162"/>
-      <c r="B35" s="273"/>
-      <c r="C35" s="280"/>
-      <c r="D35" s="265"/>
+      <c r="B35" s="282"/>
+      <c r="C35" s="290"/>
+      <c r="D35" s="289"/>
       <c r="E35" s="21">
         <v>5</v>
       </c>
@@ -18113,11 +18113,11 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="31.2">
+    <row r="36" spans="1:11" ht="19.8">
       <c r="A36" s="162"/>
-      <c r="B36" s="273"/>
-      <c r="C36" s="280"/>
-      <c r="D36" s="265"/>
+      <c r="B36" s="282"/>
+      <c r="C36" s="290"/>
+      <c r="D36" s="289"/>
       <c r="E36" s="21"/>
       <c r="F36" s="167"/>
       <c r="G36" s="168"/>
@@ -18134,9 +18134,9 @@
     </row>
     <row r="37" spans="1:11" ht="25.2" customHeight="1">
       <c r="A37" s="162"/>
-      <c r="B37" s="273"/>
-      <c r="C37" s="280"/>
-      <c r="D37" s="265"/>
+      <c r="B37" s="282"/>
+      <c r="C37" s="290"/>
+      <c r="D37" s="289"/>
       <c r="E37" s="21">
         <v>6</v>
       </c>
@@ -18155,9 +18155,9 @@
     </row>
     <row r="38" spans="1:11" ht="25.2" customHeight="1">
       <c r="A38" s="162"/>
-      <c r="B38" s="273"/>
-      <c r="C38" s="280"/>
-      <c r="D38" s="265"/>
+      <c r="B38" s="282"/>
+      <c r="C38" s="290"/>
+      <c r="D38" s="289"/>
       <c r="E38" s="21"/>
       <c r="F38" s="167"/>
       <c r="G38" s="168"/>
@@ -18172,9 +18172,9 @@
     </row>
     <row r="39" spans="1:11" ht="25.2" customHeight="1">
       <c r="A39" s="162"/>
-      <c r="B39" s="273"/>
-      <c r="C39" s="280"/>
-      <c r="D39" s="265"/>
+      <c r="B39" s="282"/>
+      <c r="C39" s="290"/>
+      <c r="D39" s="289"/>
       <c r="E39" s="21"/>
       <c r="F39" s="167"/>
       <c r="G39" s="168"/>
@@ -18189,9 +18189,9 @@
     </row>
     <row r="40" spans="1:11" ht="76.8" customHeight="1">
       <c r="A40" s="162"/>
-      <c r="B40" s="273"/>
-      <c r="C40" s="280"/>
-      <c r="D40" s="265"/>
+      <c r="B40" s="282"/>
+      <c r="C40" s="290"/>
+      <c r="D40" s="289"/>
       <c r="E40" s="21">
         <v>7</v>
       </c>
@@ -18214,11 +18214,11 @@
     </row>
     <row r="41" spans="1:11" ht="36" customHeight="1">
       <c r="A41" s="162"/>
-      <c r="B41" s="273"/>
-      <c r="C41" s="280">
+      <c r="B41" s="282"/>
+      <c r="C41" s="290">
         <v>13</v>
       </c>
-      <c r="D41" s="265" t="s">
+      <c r="D41" s="289" t="s">
         <v>304</v>
       </c>
       <c r="E41" s="21">
@@ -18245,9 +18245,9 @@
     </row>
     <row r="42" spans="1:11" ht="38.4" customHeight="1">
       <c r="A42" s="162"/>
-      <c r="B42" s="273"/>
-      <c r="C42" s="280"/>
-      <c r="D42" s="265"/>
+      <c r="B42" s="282"/>
+      <c r="C42" s="290"/>
+      <c r="D42" s="289"/>
       <c r="E42" s="21">
         <v>2</v>
       </c>
@@ -18272,11 +18272,11 @@
     </row>
     <row r="43" spans="1:11" ht="39.6">
       <c r="A43" s="162"/>
-      <c r="B43" s="273"/>
-      <c r="C43" s="280">
+      <c r="B43" s="282"/>
+      <c r="C43" s="290">
         <v>14</v>
       </c>
-      <c r="D43" s="265" t="s">
+      <c r="D43" s="289" t="s">
         <v>213</v>
       </c>
       <c r="E43" s="21">
@@ -18301,9 +18301,9 @@
     </row>
     <row r="44" spans="1:11" ht="19.8">
       <c r="A44" s="162"/>
-      <c r="B44" s="273"/>
-      <c r="C44" s="280"/>
-      <c r="D44" s="265"/>
+      <c r="B44" s="282"/>
+      <c r="C44" s="290"/>
+      <c r="D44" s="289"/>
       <c r="E44" s="21"/>
       <c r="F44" s="167"/>
       <c r="G44" s="168"/>
@@ -18314,15 +18314,15 @@
         <v>245</v>
       </c>
       <c r="J44" s="170"/>
-      <c r="K44" s="260" t="s">
+      <c r="K44" s="296" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="31.2">
       <c r="A45" s="162"/>
-      <c r="B45" s="273"/>
-      <c r="C45" s="280"/>
-      <c r="D45" s="265"/>
+      <c r="B45" s="282"/>
+      <c r="C45" s="290"/>
+      <c r="D45" s="289"/>
       <c r="E45" s="21"/>
       <c r="F45" s="167"/>
       <c r="G45" s="168"/>
@@ -18333,13 +18333,13 @@
         <v>246</v>
       </c>
       <c r="J45" s="170"/>
-      <c r="K45" s="262"/>
+      <c r="K45" s="298"/>
     </row>
     <row r="46" spans="1:11" ht="25.2" customHeight="1">
       <c r="A46" s="162"/>
-      <c r="B46" s="273"/>
-      <c r="C46" s="280"/>
-      <c r="D46" s="265"/>
+      <c r="B46" s="282"/>
+      <c r="C46" s="290"/>
+      <c r="D46" s="289"/>
       <c r="E46" s="21">
         <v>2</v>
       </c>
@@ -18362,9 +18362,9 @@
     </row>
     <row r="47" spans="1:11" ht="25.2" customHeight="1">
       <c r="A47" s="162"/>
-      <c r="B47" s="273"/>
-      <c r="C47" s="280"/>
-      <c r="D47" s="265"/>
+      <c r="B47" s="282"/>
+      <c r="C47" s="290"/>
+      <c r="D47" s="289"/>
       <c r="E47" s="21"/>
       <c r="F47" s="167"/>
       <c r="G47" s="168"/>
@@ -18375,11 +18375,11 @@
     </row>
     <row r="48" spans="1:11" ht="39.6">
       <c r="A48" s="162"/>
-      <c r="B48" s="273"/>
-      <c r="C48" s="280">
+      <c r="B48" s="282"/>
+      <c r="C48" s="290">
         <v>16</v>
       </c>
-      <c r="D48" s="265" t="s">
+      <c r="D48" s="289" t="s">
         <v>214</v>
       </c>
       <c r="E48" s="21">
@@ -18404,9 +18404,9 @@
     </row>
     <row r="49" spans="1:11" ht="25.2" customHeight="1">
       <c r="A49" s="162"/>
-      <c r="B49" s="273"/>
-      <c r="C49" s="280"/>
-      <c r="D49" s="265"/>
+      <c r="B49" s="282"/>
+      <c r="C49" s="290"/>
+      <c r="D49" s="289"/>
       <c r="E49" s="21"/>
       <c r="F49" s="167"/>
       <c r="G49" s="168"/>
@@ -18417,11 +18417,11 @@
     </row>
     <row r="50" spans="1:11" ht="25.2" customHeight="1">
       <c r="A50" s="162"/>
-      <c r="B50" s="273"/>
-      <c r="C50" s="284">
+      <c r="B50" s="282"/>
+      <c r="C50" s="294">
         <v>19</v>
       </c>
-      <c r="D50" s="281" t="s">
+      <c r="D50" s="291" t="s">
         <v>215</v>
       </c>
       <c r="E50" s="183">
@@ -18444,9 +18444,9 @@
     </row>
     <row r="51" spans="1:11" ht="25.2" customHeight="1">
       <c r="A51" s="162"/>
-      <c r="B51" s="273"/>
-      <c r="C51" s="275"/>
-      <c r="D51" s="282"/>
+      <c r="B51" s="282"/>
+      <c r="C51" s="284"/>
+      <c r="D51" s="292"/>
       <c r="E51" s="183"/>
       <c r="F51" s="22"/>
       <c r="G51" s="182"/>
@@ -18457,15 +18457,15 @@
       <c r="J51" s="170" t="s">
         <v>264</v>
       </c>
-      <c r="K51" s="260" t="s">
+      <c r="K51" s="296" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="25.2" customHeight="1">
       <c r="A52" s="162"/>
-      <c r="B52" s="273"/>
-      <c r="C52" s="275"/>
-      <c r="D52" s="282"/>
+      <c r="B52" s="282"/>
+      <c r="C52" s="284"/>
+      <c r="D52" s="292"/>
       <c r="E52" s="183"/>
       <c r="F52" s="22"/>
       <c r="G52" s="182"/>
@@ -18476,13 +18476,13 @@
       <c r="J52" s="170" t="s">
         <v>265</v>
       </c>
-      <c r="K52" s="261"/>
+      <c r="K52" s="297"/>
     </row>
     <row r="53" spans="1:11" ht="25.2" customHeight="1">
       <c r="A53" s="162"/>
-      <c r="B53" s="273"/>
-      <c r="C53" s="275"/>
-      <c r="D53" s="282"/>
+      <c r="B53" s="282"/>
+      <c r="C53" s="284"/>
+      <c r="D53" s="292"/>
       <c r="E53" s="183"/>
       <c r="F53" s="22"/>
       <c r="G53" s="182"/>
@@ -18493,13 +18493,13 @@
       <c r="J53" s="170" t="s">
         <v>266</v>
       </c>
-      <c r="K53" s="261"/>
+      <c r="K53" s="297"/>
     </row>
     <row r="54" spans="1:11" ht="31.2" customHeight="1">
       <c r="A54" s="162"/>
-      <c r="B54" s="273"/>
-      <c r="C54" s="275"/>
-      <c r="D54" s="282"/>
+      <c r="B54" s="282"/>
+      <c r="C54" s="284"/>
+      <c r="D54" s="292"/>
       <c r="E54" s="21"/>
       <c r="F54" s="167"/>
       <c r="G54" s="168"/>
@@ -18510,13 +18510,13 @@
       <c r="J54" s="187" t="s">
         <v>301</v>
       </c>
-      <c r="K54" s="262"/>
+      <c r="K54" s="298"/>
     </row>
     <row r="55" spans="1:11" ht="24" customHeight="1" thickBot="1">
       <c r="A55" s="162"/>
-      <c r="B55" s="274"/>
-      <c r="C55" s="285"/>
-      <c r="D55" s="283"/>
+      <c r="B55" s="283"/>
+      <c r="C55" s="295"/>
+      <c r="D55" s="293"/>
       <c r="E55" s="171"/>
       <c r="F55" s="172"/>
       <c r="G55" s="173"/>
@@ -18529,30 +18529,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="K51:K54"/>
-    <mergeCell ref="K32:K34"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="D43:D47"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C19:C40"/>
-    <mergeCell ref="D19:D40"/>
-    <mergeCell ref="K7:K11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="B5:B55"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="D7:D12"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="C50:C55"/>
-    <mergeCell ref="D50:D55"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -18564,6 +18540,30 @@
     <mergeCell ref="H3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:B55"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="D7:D12"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="C50:C55"/>
+    <mergeCell ref="D50:D55"/>
+    <mergeCell ref="K7:K11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="K51:K54"/>
+    <mergeCell ref="K32:K34"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="D43:D47"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C19:C40"/>
+    <mergeCell ref="D19:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18576,71 +18576,71 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:AX83"/>
-  <sheetFormatPr defaultColWidth="7.33203125" defaultRowHeight="20.399999999999999"/>
+  <sheetFormatPr defaultColWidth="7.296875" defaultRowHeight="20.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="160" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="160" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" style="160" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="160" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" style="160" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" style="160" customWidth="1"/>
-    <col min="7" max="9" width="15.33203125" style="160" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" style="160" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" style="160" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" style="160" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="160" customWidth="1"/>
+    <col min="1" max="1" width="7.09765625" style="160" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" style="160" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="160" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="160" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" style="160" customWidth="1"/>
+    <col min="6" max="6" width="13.8984375" style="160" customWidth="1"/>
+    <col min="7" max="9" width="15.296875" style="160" customWidth="1"/>
+    <col min="10" max="10" width="13.09765625" style="160" customWidth="1"/>
+    <col min="11" max="11" width="15.09765625" style="160" customWidth="1"/>
+    <col min="12" max="12" width="13.296875" style="160" customWidth="1"/>
+    <col min="13" max="13" width="15.3984375" style="160" customWidth="1"/>
     <col min="14" max="14" width="33" style="160" customWidth="1"/>
-    <col min="15" max="15" width="33.77734375" style="157" customWidth="1"/>
-    <col min="16" max="16" width="6.21875" style="157" customWidth="1"/>
-    <col min="17" max="19" width="3.109375" style="157" customWidth="1"/>
-    <col min="20" max="20" width="21.33203125" style="157" customWidth="1"/>
-    <col min="21" max="23" width="6.44140625" style="33" customWidth="1"/>
-    <col min="24" max="16384" width="7.33203125" style="160"/>
+    <col min="15" max="15" width="33.796875" style="157" customWidth="1"/>
+    <col min="16" max="16" width="6.19921875" style="157" customWidth="1"/>
+    <col min="17" max="19" width="3.09765625" style="157" customWidth="1"/>
+    <col min="20" max="20" width="21.296875" style="157" customWidth="1"/>
+    <col min="21" max="23" width="6.3984375" style="33" customWidth="1"/>
+    <col min="24" max="16384" width="7.296875" style="160"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="26" customFormat="1" ht="26.4">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="348" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="312"/>
-      <c r="D1" s="313" t="s">
+      <c r="B1" s="349"/>
+      <c r="C1" s="350"/>
+      <c r="D1" s="351" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="314"/>
-      <c r="F1" s="314"/>
-      <c r="G1" s="314"/>
-      <c r="H1" s="314"/>
-      <c r="I1" s="314"/>
-      <c r="J1" s="314"/>
-      <c r="K1" s="314"/>
-      <c r="L1" s="314"/>
-      <c r="M1" s="314"/>
-      <c r="N1" s="314"/>
+      <c r="E1" s="352"/>
+      <c r="F1" s="352"/>
+      <c r="G1" s="352"/>
+      <c r="H1" s="352"/>
+      <c r="I1" s="352"/>
+      <c r="J1" s="352"/>
+      <c r="K1" s="352"/>
+      <c r="L1" s="352"/>
+      <c r="M1" s="352"/>
+      <c r="N1" s="352"/>
       <c r="O1" s="24"/>
       <c r="P1" s="25"/>
       <c r="Q1" s="25"/>
-      <c r="R1" s="315" t="s">
+      <c r="R1" s="353" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="315"/>
-      <c r="T1" s="315"/>
-      <c r="U1" s="315"/>
-      <c r="V1" s="316" t="s">
+      <c r="S1" s="353"/>
+      <c r="T1" s="353"/>
+      <c r="U1" s="353"/>
+      <c r="V1" s="315" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="317"/>
+      <c r="W1" s="314"/>
     </row>
     <row r="2" spans="1:50" s="29" customFormat="1" ht="24.75" customHeight="1">
       <c r="A2" s="27"/>
       <c r="B2" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="318" t="s">
+      <c r="C2" s="354" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="318"/>
-      <c r="E2" s="318"/>
+      <c r="D2" s="354"/>
+      <c r="E2" s="354"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -18655,16 +18655,16 @@
       </c>
       <c r="P2" s="24"/>
       <c r="Q2" s="25"/>
-      <c r="R2" s="319" t="s">
+      <c r="R2" s="355" t="s">
         <v>74</v>
       </c>
-      <c r="S2" s="319"/>
-      <c r="T2" s="319"/>
-      <c r="U2" s="319"/>
-      <c r="V2" s="320">
+      <c r="S2" s="355"/>
+      <c r="T2" s="355"/>
+      <c r="U2" s="355"/>
+      <c r="V2" s="356">
         <v>43175</v>
       </c>
-      <c r="W2" s="321"/>
+      <c r="W2" s="357"/>
     </row>
     <row r="3" spans="1:50" s="29" customFormat="1" ht="3" customHeight="1">
       <c r="A3" s="30"/>
@@ -18694,7 +18694,7 @@
       <c r="W3" s="34"/>
     </row>
     <row r="4" spans="1:50" s="29" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="322" t="s">
+      <c r="A4" s="339" t="s">
         <v>76</v>
       </c>
       <c r="B4" s="35"/>
@@ -18713,19 +18713,19 @@
       <c r="O4" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="323" t="s">
+      <c r="P4" s="340" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="323"/>
-      <c r="R4" s="323"/>
-      <c r="S4" s="323"/>
-      <c r="T4" s="323"/>
-      <c r="U4" s="323"/>
-      <c r="V4" s="323"/>
-      <c r="W4" s="323"/>
+      <c r="Q4" s="340"/>
+      <c r="R4" s="340"/>
+      <c r="S4" s="340"/>
+      <c r="T4" s="340"/>
+      <c r="U4" s="340"/>
+      <c r="V4" s="340"/>
+      <c r="W4" s="340"/>
     </row>
     <row r="5" spans="1:50" s="47" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="322"/>
+      <c r="A5" s="339"/>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
@@ -18781,7 +18781,7 @@
       <c r="AX5" s="46"/>
     </row>
     <row r="6" spans="1:50" s="47" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="322"/>
+      <c r="A6" s="339"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="38"/>
@@ -18837,7 +18837,7 @@
       <c r="AX6" s="46"/>
     </row>
     <row r="7" spans="1:50" s="47" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="322"/>
+      <c r="A7" s="339"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
       <c r="D7" s="38"/>
@@ -18891,7 +18891,7 @@
       <c r="AX7" s="46"/>
     </row>
     <row r="8" spans="1:50" s="47" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="322"/>
+      <c r="A8" s="339"/>
       <c r="B8" s="38"/>
       <c r="C8" s="38"/>
       <c r="D8" s="38"/>
@@ -18945,7 +18945,7 @@
       <c r="AX8" s="46"/>
     </row>
     <row r="9" spans="1:50" s="47" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="322"/>
+      <c r="A9" s="339"/>
       <c r="B9" s="56"/>
       <c r="C9" s="56"/>
       <c r="D9" s="56"/>
@@ -18972,85 +18972,85 @@
       <c r="W9" s="62"/>
     </row>
     <row r="10" spans="1:50" s="29" customFormat="1" ht="24.45" customHeight="1">
-      <c r="A10" s="324" t="s">
+      <c r="A10" s="341" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="326" t="s">
+      <c r="B10" s="337" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="326" t="s">
+      <c r="C10" s="337" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="326" t="s">
+      <c r="D10" s="337" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="326" t="s">
+      <c r="E10" s="337" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="326" t="s">
+      <c r="F10" s="337" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="326" t="s">
+      <c r="G10" s="337" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="328" t="s">
+      <c r="H10" s="343" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="326" t="s">
+      <c r="I10" s="337" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="326" t="s">
+      <c r="J10" s="337" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="326" t="s">
+      <c r="K10" s="337" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="326" t="s">
+      <c r="L10" s="337" t="s">
         <v>97</v>
       </c>
-      <c r="M10" s="326" t="s">
+      <c r="M10" s="337" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="331" t="s">
+      <c r="N10" s="346" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="346" t="s">
+      <c r="O10" s="324" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="348" t="s">
+      <c r="P10" s="326" t="s">
         <v>101</v>
       </c>
-      <c r="Q10" s="349"/>
-      <c r="R10" s="349"/>
-      <c r="S10" s="349"/>
-      <c r="T10" s="349"/>
-      <c r="U10" s="330" t="s">
+      <c r="Q10" s="327"/>
+      <c r="R10" s="327"/>
+      <c r="S10" s="327"/>
+      <c r="T10" s="327"/>
+      <c r="U10" s="345" t="s">
         <v>102</v>
       </c>
-      <c r="V10" s="330"/>
-      <c r="W10" s="330"/>
+      <c r="V10" s="345"/>
+      <c r="W10" s="345"/>
     </row>
     <row r="11" spans="1:50" s="29" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A11" s="325"/>
-      <c r="B11" s="327"/>
-      <c r="C11" s="327"/>
-      <c r="D11" s="327"/>
-      <c r="E11" s="327"/>
-      <c r="F11" s="327"/>
-      <c r="G11" s="327"/>
-      <c r="H11" s="329"/>
-      <c r="I11" s="327"/>
-      <c r="J11" s="327"/>
-      <c r="K11" s="327"/>
-      <c r="L11" s="327"/>
-      <c r="M11" s="327"/>
-      <c r="N11" s="332"/>
-      <c r="O11" s="347"/>
-      <c r="P11" s="350"/>
-      <c r="Q11" s="351"/>
-      <c r="R11" s="351"/>
-      <c r="S11" s="351"/>
-      <c r="T11" s="351"/>
+      <c r="A11" s="342"/>
+      <c r="B11" s="338"/>
+      <c r="C11" s="338"/>
+      <c r="D11" s="338"/>
+      <c r="E11" s="338"/>
+      <c r="F11" s="338"/>
+      <c r="G11" s="338"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="338"/>
+      <c r="J11" s="338"/>
+      <c r="K11" s="338"/>
+      <c r="L11" s="338"/>
+      <c r="M11" s="338"/>
+      <c r="N11" s="347"/>
+      <c r="O11" s="325"/>
+      <c r="P11" s="328"/>
+      <c r="Q11" s="329"/>
+      <c r="R11" s="329"/>
+      <c r="S11" s="329"/>
+      <c r="T11" s="329"/>
       <c r="U11" s="63" t="s">
         <v>103</v>
       </c>
@@ -19093,7 +19093,7 @@
       <c r="W12" s="72"/>
     </row>
     <row r="13" spans="1:50" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A13" s="334"/>
+      <c r="A13" s="331"/>
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
       <c r="D13" s="74"/>
@@ -19118,7 +19118,7 @@
       <c r="W13" s="81"/>
     </row>
     <row r="14" spans="1:50" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A14" s="334"/>
+      <c r="A14" s="331"/>
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -19142,7 +19142,7 @@
       <c r="W14" s="83"/>
     </row>
     <row r="15" spans="1:50" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A15" s="334"/>
+      <c r="A15" s="331"/>
       <c r="B15" s="74"/>
       <c r="C15" s="74"/>
       <c r="D15" s="74"/>
@@ -19175,7 +19175,7 @@
       <c r="W15" s="83"/>
     </row>
     <row r="16" spans="1:50" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A16" s="334"/>
+      <c r="A16" s="331"/>
       <c r="B16" s="74"/>
       <c r="C16" s="74"/>
       <c r="D16" s="74"/>
@@ -19204,7 +19204,7 @@
       <c r="W16" s="89"/>
     </row>
     <row r="17" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A17" s="334"/>
+      <c r="A17" s="331"/>
       <c r="B17" s="74"/>
       <c r="C17" s="74"/>
       <c r="D17" s="74"/>
@@ -19233,7 +19233,7 @@
       <c r="W17" s="81"/>
     </row>
     <row r="18" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A18" s="335"/>
+      <c r="A18" s="332"/>
       <c r="B18" s="91"/>
       <c r="C18" s="91"/>
       <c r="D18" s="91"/>
@@ -19262,7 +19262,7 @@
       <c r="W18" s="97"/>
     </row>
     <row r="19" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A19" s="336" t="s">
+      <c r="A19" s="334" t="s">
         <v>117</v>
       </c>
       <c r="B19" s="65"/>
@@ -19297,7 +19297,7 @@
       <c r="W19" s="103"/>
     </row>
     <row r="20" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A20" s="337"/>
+      <c r="A20" s="335"/>
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
@@ -19330,7 +19330,7 @@
       <c r="W20" s="83"/>
     </row>
     <row r="21" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A21" s="337"/>
+      <c r="A21" s="335"/>
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
       <c r="D21" s="74"/>
@@ -19357,7 +19357,7 @@
       <c r="W21" s="107"/>
     </row>
     <row r="22" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A22" s="337"/>
+      <c r="A22" s="335"/>
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -19384,7 +19384,7 @@
       <c r="W22" s="81"/>
     </row>
     <row r="23" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A23" s="337"/>
+      <c r="A23" s="335"/>
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
@@ -19411,7 +19411,7 @@
       <c r="W23" s="83"/>
     </row>
     <row r="24" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A24" s="337"/>
+      <c r="A24" s="335"/>
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
       <c r="D24" s="74"/>
@@ -19438,7 +19438,7 @@
       <c r="W24" s="83"/>
     </row>
     <row r="25" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A25" s="337"/>
+      <c r="A25" s="335"/>
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
       <c r="D25" s="74"/>
@@ -19465,7 +19465,7 @@
       <c r="W25" s="83"/>
     </row>
     <row r="26" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A26" s="337"/>
+      <c r="A26" s="335"/>
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
@@ -19492,7 +19492,7 @@
       <c r="W26" s="83"/>
     </row>
     <row r="27" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A27" s="337"/>
+      <c r="A27" s="335"/>
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
       <c r="D27" s="74"/>
@@ -19519,7 +19519,7 @@
       <c r="W27" s="81"/>
     </row>
     <row r="28" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A28" s="337"/>
+      <c r="A28" s="335"/>
       <c r="B28" s="74"/>
       <c r="C28" s="74"/>
       <c r="D28" s="74"/>
@@ -19545,7 +19545,7 @@
       <c r="W28" s="81"/>
     </row>
     <row r="29" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A29" s="337"/>
+      <c r="A29" s="335"/>
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
       <c r="D29" s="74"/>
@@ -19572,7 +19572,7 @@
       <c r="W29" s="108"/>
     </row>
     <row r="30" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A30" s="337"/>
+      <c r="A30" s="335"/>
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
       <c r="D30" s="74"/>
@@ -19597,7 +19597,7 @@
       <c r="W30" s="83"/>
     </row>
     <row r="31" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A31" s="337"/>
+      <c r="A31" s="335"/>
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
@@ -19624,7 +19624,7 @@
       <c r="W31" s="83"/>
     </row>
     <row r="32" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A32" s="337"/>
+      <c r="A32" s="335"/>
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
@@ -19651,7 +19651,7 @@
       <c r="W32" s="83"/>
     </row>
     <row r="33" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A33" s="338"/>
+      <c r="A33" s="336"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
       <c r="D33" s="91"/>
@@ -19678,7 +19678,7 @@
       <c r="W33" s="113"/>
     </row>
     <row r="34" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A34" s="336" t="s">
+      <c r="A34" s="334" t="s">
         <v>134</v>
       </c>
       <c r="B34" s="74"/>
@@ -19707,7 +19707,7 @@
       <c r="W34" s="83"/>
     </row>
     <row r="35" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A35" s="337"/>
+      <c r="A35" s="335"/>
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
       <c r="D35" s="74"/>
@@ -19740,7 +19740,7 @@
       <c r="W35" s="83"/>
     </row>
     <row r="36" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A36" s="337"/>
+      <c r="A36" s="335"/>
       <c r="B36" s="74"/>
       <c r="C36" s="74"/>
       <c r="D36" s="74"/>
@@ -19769,7 +19769,7 @@
       <c r="W36" s="108"/>
     </row>
     <row r="37" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A37" s="337"/>
+      <c r="A37" s="335"/>
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
@@ -19798,7 +19798,7 @@
       <c r="W37" s="108"/>
     </row>
     <row r="38" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A38" s="337"/>
+      <c r="A38" s="335"/>
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
       <c r="D38" s="74"/>
@@ -19827,7 +19827,7 @@
       <c r="W38" s="108"/>
     </row>
     <row r="39" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A39" s="337"/>
+      <c r="A39" s="335"/>
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
       <c r="D39" s="74"/>
@@ -19856,7 +19856,7 @@
       <c r="W39" s="108"/>
     </row>
     <row r="40" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A40" s="337"/>
+      <c r="A40" s="335"/>
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
       <c r="D40" s="74"/>
@@ -19885,7 +19885,7 @@
       <c r="W40" s="108"/>
     </row>
     <row r="41" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A41" s="337"/>
+      <c r="A41" s="335"/>
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
       <c r="D41" s="74"/>
@@ -19910,7 +19910,7 @@
       <c r="W41" s="108"/>
     </row>
     <row r="42" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A42" s="337"/>
+      <c r="A42" s="335"/>
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
       <c r="D42" s="74"/>
@@ -19941,7 +19941,7 @@
       <c r="W42" s="81"/>
     </row>
     <row r="43" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A43" s="337"/>
+      <c r="A43" s="335"/>
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
       <c r="D43" s="74"/>
@@ -19974,7 +19974,7 @@
       <c r="W43" s="81"/>
     </row>
     <row r="44" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A44" s="337"/>
+      <c r="A44" s="335"/>
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
       <c r="D44" s="74"/>
@@ -20001,7 +20001,7 @@
       <c r="W44" s="81"/>
     </row>
     <row r="45" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A45" s="337"/>
+      <c r="A45" s="335"/>
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
       <c r="D45" s="74"/>
@@ -20038,7 +20038,7 @@
       </c>
     </row>
     <row r="46" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A46" s="337"/>
+      <c r="A46" s="335"/>
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
@@ -20067,7 +20067,7 @@
       <c r="W46" s="81"/>
     </row>
     <row r="47" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A47" s="337"/>
+      <c r="A47" s="335"/>
       <c r="B47" s="74"/>
       <c r="C47" s="74"/>
       <c r="D47" s="74"/>
@@ -20096,7 +20096,7 @@
       <c r="W47" s="81"/>
     </row>
     <row r="48" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A48" s="337"/>
+      <c r="A48" s="335"/>
       <c r="B48" s="74"/>
       <c r="C48" s="74"/>
       <c r="D48" s="74"/>
@@ -20123,7 +20123,7 @@
       <c r="W48" s="81"/>
     </row>
     <row r="49" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A49" s="337"/>
+      <c r="A49" s="335"/>
       <c r="B49" s="74"/>
       <c r="C49" s="74"/>
       <c r="D49" s="74"/>
@@ -20152,7 +20152,7 @@
       <c r="W49" s="81"/>
     </row>
     <row r="50" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A50" s="337"/>
+      <c r="A50" s="335"/>
       <c r="B50" s="74"/>
       <c r="C50" s="74"/>
       <c r="D50" s="74"/>
@@ -20181,7 +20181,7 @@
       <c r="W50" s="81"/>
     </row>
     <row r="51" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A51" s="337"/>
+      <c r="A51" s="335"/>
       <c r="B51" s="74"/>
       <c r="C51" s="74"/>
       <c r="D51" s="74"/>
@@ -20208,7 +20208,7 @@
       <c r="W51" s="81"/>
     </row>
     <row r="52" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A52" s="337"/>
+      <c r="A52" s="335"/>
       <c r="B52" s="74"/>
       <c r="C52" s="74"/>
       <c r="D52" s="74"/>
@@ -20235,7 +20235,7 @@
       <c r="W52" s="81"/>
     </row>
     <row r="53" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A53" s="338"/>
+      <c r="A53" s="336"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
       <c r="D53" s="91"/>
@@ -20260,7 +20260,7 @@
       <c r="W53" s="113"/>
     </row>
     <row r="54" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A54" s="352" t="s">
+      <c r="A54" s="330" t="s">
         <v>160</v>
       </c>
       <c r="B54" s="74"/>
@@ -20295,7 +20295,7 @@
       <c r="W54" s="81"/>
     </row>
     <row r="55" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A55" s="352"/>
+      <c r="A55" s="330"/>
       <c r="B55" s="74"/>
       <c r="C55" s="74"/>
       <c r="D55" s="74"/>
@@ -20324,7 +20324,7 @@
       <c r="W55" s="108"/>
     </row>
     <row r="56" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A56" s="352"/>
+      <c r="A56" s="330"/>
       <c r="B56" s="74"/>
       <c r="C56" s="74"/>
       <c r="D56" s="74"/>
@@ -20351,7 +20351,7 @@
       <c r="W56" s="108"/>
     </row>
     <row r="57" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A57" s="352"/>
+      <c r="A57" s="330"/>
       <c r="B57" s="74"/>
       <c r="C57" s="74"/>
       <c r="D57" s="74"/>
@@ -20378,7 +20378,7 @@
       <c r="W57" s="83"/>
     </row>
     <row r="58" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A58" s="352"/>
+      <c r="A58" s="330"/>
       <c r="B58" s="74"/>
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
@@ -20405,7 +20405,7 @@
       <c r="W58" s="83"/>
     </row>
     <row r="59" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A59" s="352"/>
+      <c r="A59" s="330"/>
       <c r="B59" s="74"/>
       <c r="C59" s="74"/>
       <c r="D59" s="74"/>
@@ -20432,7 +20432,7 @@
       <c r="W59" s="83"/>
     </row>
     <row r="60" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A60" s="352"/>
+      <c r="A60" s="330"/>
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
       <c r="D60" s="74"/>
@@ -20459,7 +20459,7 @@
       <c r="W60" s="107"/>
     </row>
     <row r="61" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A61" s="352"/>
+      <c r="A61" s="330"/>
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
       <c r="D61" s="74"/>
@@ -20488,7 +20488,7 @@
       <c r="W61" s="107"/>
     </row>
     <row r="62" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A62" s="352"/>
+      <c r="A62" s="330"/>
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
       <c r="D62" s="74"/>
@@ -20517,7 +20517,7 @@
       <c r="W62" s="81"/>
     </row>
     <row r="63" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A63" s="352"/>
+      <c r="A63" s="330"/>
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
       <c r="D63" s="74"/>
@@ -20546,7 +20546,7 @@
       <c r="W63" s="81"/>
     </row>
     <row r="64" spans="1:23" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A64" s="352"/>
+      <c r="A64" s="330"/>
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
       <c r="D64" s="74"/>
@@ -20575,7 +20575,7 @@
       <c r="W64" s="126"/>
     </row>
     <row r="65" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A65" s="352"/>
+      <c r="A65" s="330"/>
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
       <c r="D65" s="74"/>
@@ -20602,7 +20602,7 @@
       <c r="W65" s="126"/>
     </row>
     <row r="66" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A66" s="352"/>
+      <c r="A66" s="330"/>
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
       <c r="D66" s="74"/>
@@ -20629,7 +20629,7 @@
       <c r="W66" s="83"/>
     </row>
     <row r="67" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A67" s="352"/>
+      <c r="A67" s="330"/>
       <c r="B67" s="74"/>
       <c r="C67" s="74"/>
       <c r="D67" s="74"/>
@@ -20658,7 +20658,7 @@
       <c r="W67" s="81"/>
     </row>
     <row r="68" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A68" s="352"/>
+      <c r="A68" s="330"/>
       <c r="B68" s="74"/>
       <c r="C68" s="74"/>
       <c r="D68" s="74"/>
@@ -20683,7 +20683,7 @@
       <c r="W68" s="81"/>
     </row>
     <row r="69" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A69" s="352"/>
+      <c r="A69" s="330"/>
       <c r="B69" s="74"/>
       <c r="C69" s="74"/>
       <c r="D69" s="74"/>
@@ -20708,7 +20708,7 @@
       <c r="W69" s="81"/>
     </row>
     <row r="70" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A70" s="352"/>
+      <c r="A70" s="330"/>
       <c r="B70" s="74"/>
       <c r="C70" s="74"/>
       <c r="D70" s="74"/>
@@ -20741,7 +20741,7 @@
       <c r="W70" s="81"/>
     </row>
     <row r="71" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A71" s="334"/>
+      <c r="A71" s="331"/>
       <c r="B71" s="74"/>
       <c r="C71" s="74"/>
       <c r="D71" s="74"/>
@@ -20772,7 +20772,7 @@
       <c r="W71" s="81"/>
     </row>
     <row r="72" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A72" s="334"/>
+      <c r="A72" s="331"/>
       <c r="B72" s="74"/>
       <c r="C72" s="74"/>
       <c r="D72" s="74"/>
@@ -20801,7 +20801,7 @@
       </c>
     </row>
     <row r="73" spans="1:25" s="73" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A73" s="335"/>
+      <c r="A73" s="332"/>
       <c r="B73" s="91"/>
       <c r="C73" s="91"/>
       <c r="D73" s="91"/>
@@ -20851,7 +20851,7 @@
       <c r="R74" s="135"/>
       <c r="S74" s="135"/>
       <c r="T74" s="136"/>
-      <c r="U74" s="354"/>
+      <c r="U74" s="311"/>
       <c r="V74" s="137"/>
       <c r="W74" s="137"/>
       <c r="Y74" s="73"/>
@@ -20883,11 +20883,11 @@
       <c r="P75" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="Q75" s="356"/>
-      <c r="R75" s="356"/>
-      <c r="S75" s="356"/>
-      <c r="T75" s="357"/>
-      <c r="U75" s="355"/>
+      <c r="Q75" s="319"/>
+      <c r="R75" s="319"/>
+      <c r="S75" s="319"/>
+      <c r="T75" s="320"/>
+      <c r="U75" s="312"/>
       <c r="V75" s="143"/>
       <c r="W75" s="143"/>
       <c r="Y75" s="73"/>
@@ -20923,7 +20923,7 @@
       <c r="R76" s="145"/>
       <c r="S76" s="146"/>
       <c r="T76" s="147"/>
-      <c r="U76" s="355"/>
+      <c r="U76" s="312"/>
       <c r="V76" s="143"/>
       <c r="W76" s="143"/>
       <c r="Y76" s="73"/>
@@ -20951,7 +20951,7 @@
       <c r="R77" s="146"/>
       <c r="S77" s="146"/>
       <c r="T77" s="147"/>
-      <c r="U77" s="355"/>
+      <c r="U77" s="312"/>
       <c r="V77" s="143"/>
       <c r="W77" s="143"/>
       <c r="Y77" s="73"/>
@@ -20974,11 +20974,11 @@
       <c r="M78" s="149"/>
       <c r="N78" s="149"/>
       <c r="O78" s="151"/>
-      <c r="P78" s="343"/>
-      <c r="Q78" s="344"/>
-      <c r="R78" s="344"/>
-      <c r="S78" s="344"/>
-      <c r="T78" s="345"/>
+      <c r="P78" s="321"/>
+      <c r="Q78" s="322"/>
+      <c r="R78" s="322"/>
+      <c r="S78" s="322"/>
+      <c r="T78" s="323"/>
       <c r="U78" s="152"/>
       <c r="V78" s="153"/>
       <c r="W78" s="153"/>
@@ -21010,122 +21010,141 @@
       <c r="W79" s="33"/>
     </row>
     <row r="80" spans="1:25" s="145" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A80" s="342" t="s">
+      <c r="A80" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="B80" s="316"/>
-      <c r="C80" s="317"/>
-      <c r="D80" s="342" t="s">
+      <c r="B80" s="315"/>
+      <c r="C80" s="314"/>
+      <c r="D80" s="313" t="s">
         <v>198</v>
       </c>
-      <c r="E80" s="316"/>
-      <c r="F80" s="316"/>
-      <c r="G80" s="317"/>
-      <c r="H80" s="342" t="s">
+      <c r="E80" s="315"/>
+      <c r="F80" s="315"/>
+      <c r="G80" s="314"/>
+      <c r="H80" s="313" t="s">
         <v>199</v>
       </c>
-      <c r="I80" s="316"/>
-      <c r="J80" s="316"/>
-      <c r="K80" s="316"/>
-      <c r="L80" s="316"/>
-      <c r="M80" s="317"/>
-      <c r="N80" s="342" t="s">
+      <c r="I80" s="315"/>
+      <c r="J80" s="315"/>
+      <c r="K80" s="315"/>
+      <c r="L80" s="315"/>
+      <c r="M80" s="314"/>
+      <c r="N80" s="313" t="s">
         <v>200</v>
       </c>
-      <c r="O80" s="317"/>
-      <c r="P80" s="342" t="s">
+      <c r="O80" s="314"/>
+      <c r="P80" s="313" t="s">
         <v>201</v>
       </c>
-      <c r="Q80" s="316"/>
-      <c r="R80" s="316"/>
-      <c r="S80" s="316"/>
-      <c r="T80" s="316"/>
-      <c r="U80" s="316"/>
-      <c r="V80" s="316"/>
-      <c r="W80" s="317"/>
+      <c r="Q80" s="315"/>
+      <c r="R80" s="315"/>
+      <c r="S80" s="315"/>
+      <c r="T80" s="315"/>
+      <c r="U80" s="315"/>
+      <c r="V80" s="315"/>
+      <c r="W80" s="314"/>
     </row>
     <row r="81" spans="1:23" s="145" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A81" s="339"/>
-      <c r="B81" s="340"/>
-      <c r="C81" s="341"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="316"/>
-      <c r="F81" s="316"/>
-      <c r="G81" s="317"/>
-      <c r="H81" s="342"/>
-      <c r="I81" s="316"/>
-      <c r="J81" s="316"/>
-      <c r="K81" s="316"/>
-      <c r="L81" s="316"/>
-      <c r="M81" s="317"/>
-      <c r="N81" s="339"/>
-      <c r="O81" s="341"/>
-      <c r="P81" s="339"/>
-      <c r="Q81" s="340"/>
-      <c r="R81" s="340"/>
-      <c r="S81" s="340"/>
-      <c r="T81" s="340"/>
-      <c r="U81" s="340"/>
-      <c r="V81" s="340"/>
-      <c r="W81" s="341"/>
+      <c r="A81" s="316"/>
+      <c r="B81" s="318"/>
+      <c r="C81" s="317"/>
+      <c r="D81" s="313"/>
+      <c r="E81" s="315"/>
+      <c r="F81" s="315"/>
+      <c r="G81" s="314"/>
+      <c r="H81" s="313"/>
+      <c r="I81" s="315"/>
+      <c r="J81" s="315"/>
+      <c r="K81" s="315"/>
+      <c r="L81" s="315"/>
+      <c r="M81" s="314"/>
+      <c r="N81" s="316"/>
+      <c r="O81" s="317"/>
+      <c r="P81" s="316"/>
+      <c r="Q81" s="318"/>
+      <c r="R81" s="318"/>
+      <c r="S81" s="318"/>
+      <c r="T81" s="318"/>
+      <c r="U81" s="318"/>
+      <c r="V81" s="318"/>
+      <c r="W81" s="317"/>
     </row>
     <row r="82" spans="1:23" s="145" customFormat="1" ht="36.9" customHeight="1">
-      <c r="A82" s="339" t="s">
+      <c r="A82" s="316" t="s">
         <v>202</v>
       </c>
-      <c r="B82" s="340"/>
-      <c r="C82" s="341"/>
-      <c r="D82" s="342" t="s">
+      <c r="B82" s="318"/>
+      <c r="C82" s="317"/>
+      <c r="D82" s="313" t="s">
         <v>202</v>
       </c>
-      <c r="E82" s="316"/>
-      <c r="F82" s="316"/>
-      <c r="G82" s="317"/>
-      <c r="H82" s="342" t="s">
+      <c r="E82" s="315"/>
+      <c r="F82" s="315"/>
+      <c r="G82" s="314"/>
+      <c r="H82" s="313" t="s">
         <v>202</v>
       </c>
-      <c r="I82" s="316"/>
-      <c r="J82" s="316"/>
-      <c r="K82" s="316"/>
-      <c r="L82" s="316"/>
-      <c r="M82" s="317"/>
-      <c r="N82" s="339" t="s">
+      <c r="I82" s="315"/>
+      <c r="J82" s="315"/>
+      <c r="K82" s="315"/>
+      <c r="L82" s="315"/>
+      <c r="M82" s="314"/>
+      <c r="N82" s="316" t="s">
         <v>202</v>
       </c>
-      <c r="O82" s="341"/>
-      <c r="P82" s="339" t="s">
+      <c r="O82" s="317"/>
+      <c r="P82" s="316" t="s">
         <v>202</v>
       </c>
-      <c r="Q82" s="340"/>
-      <c r="R82" s="340"/>
-      <c r="S82" s="340"/>
-      <c r="T82" s="340"/>
-      <c r="U82" s="340"/>
-      <c r="V82" s="340"/>
-      <c r="W82" s="341"/>
+      <c r="Q82" s="318"/>
+      <c r="R82" s="318"/>
+      <c r="S82" s="318"/>
+      <c r="T82" s="318"/>
+      <c r="U82" s="318"/>
+      <c r="V82" s="318"/>
+      <c r="W82" s="317"/>
     </row>
     <row r="83" spans="1:23" s="158" customFormat="1" ht="30.75" customHeight="1">
       <c r="N83" s="159"/>
       <c r="O83" s="33"/>
       <c r="P83" s="157"/>
       <c r="Q83" s="157"/>
-      <c r="R83" s="353"/>
-      <c r="S83" s="353"/>
-      <c r="T83" s="353"/>
-      <c r="U83" s="353"/>
-      <c r="V83" s="353"/>
-      <c r="W83" s="353"/>
+      <c r="R83" s="310"/>
+      <c r="S83" s="310"/>
+      <c r="T83" s="310"/>
+      <c r="U83" s="310"/>
+      <c r="V83" s="310"/>
+      <c r="W83" s="310"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="R83:W83"/>
-    <mergeCell ref="U74:U75"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="P80:W80"/>
-    <mergeCell ref="N82:O82"/>
-    <mergeCell ref="P82:W82"/>
-    <mergeCell ref="Q75:T75"/>
-    <mergeCell ref="U76:U77"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:N1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="P4:W4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="A19:A33"/>
+    <mergeCell ref="A34:A53"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="D82:G82"/>
     <mergeCell ref="H82:M82"/>
@@ -21142,33 +21161,14 @@
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="D80:G80"/>
     <mergeCell ref="H80:M80"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="A19:A33"/>
-    <mergeCell ref="A34:A53"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="P4:W4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:N1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="R83:W83"/>
+    <mergeCell ref="U74:U75"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="P80:W80"/>
+    <mergeCell ref="N82:O82"/>
+    <mergeCell ref="P82:W82"/>
+    <mergeCell ref="Q75:T75"/>
+    <mergeCell ref="U76:U77"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
@@ -21190,107 +21190,107 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:K55"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" style="161" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" style="161" customWidth="1"/>
     <col min="2" max="2" width="18" style="19" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="192" customWidth="1"/>
-    <col min="4" max="4" width="29.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="3.6640625" style="176" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" style="19" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="161" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" style="176" customWidth="1"/>
-    <col min="9" max="9" width="39.44140625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" style="19" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="19" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="19"/>
+    <col min="3" max="3" width="3.69921875" style="192" customWidth="1"/>
+    <col min="4" max="4" width="29.3984375" style="19" customWidth="1"/>
+    <col min="5" max="5" width="3.69921875" style="176" customWidth="1"/>
+    <col min="6" max="6" width="30.09765625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="12.796875" style="161" customWidth="1"/>
+    <col min="8" max="8" width="3.69921875" style="176" customWidth="1"/>
+    <col min="9" max="9" width="39.3984375" style="19" customWidth="1"/>
+    <col min="10" max="10" width="19.69921875" style="19" customWidth="1"/>
+    <col min="11" max="11" width="39.3984375" style="19" customWidth="1"/>
+    <col min="12" max="16384" width="8.69921875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.4" thickBot="1">
-      <c r="A1" s="286" t="s">
+      <c r="A1" s="260" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="286"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="286"/>
-      <c r="E1" s="286"/>
-      <c r="F1" s="286"/>
-      <c r="G1" s="286"/>
-      <c r="H1" s="286"/>
-      <c r="I1" s="286"/>
-      <c r="J1" s="286"/>
-      <c r="K1" s="286"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
     </row>
     <row r="2" spans="1:11" ht="44.55" customHeight="1" thickBot="1">
       <c r="A2" s="217"/>
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="261" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="288"/>
-      <c r="D2" s="288"/>
-      <c r="E2" s="288"/>
-      <c r="F2" s="288"/>
-      <c r="G2" s="289"/>
-      <c r="H2" s="290" t="s">
+      <c r="C2" s="262"/>
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="291"/>
-      <c r="J2" s="291"/>
-      <c r="K2" s="358"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" s="20" customFormat="1" ht="21.6" customHeight="1">
-      <c r="A3" s="359" t="s">
+      <c r="A3" s="368" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="293" t="s">
+      <c r="B3" s="267" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="295" t="s">
+      <c r="C3" s="269" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="296"/>
-      <c r="E3" s="295" t="s">
+      <c r="D3" s="270"/>
+      <c r="E3" s="269" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="296"/>
-      <c r="G3" s="299" t="s">
+      <c r="F3" s="270"/>
+      <c r="G3" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="360" t="s">
+      <c r="H3" s="369" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="302"/>
-      <c r="J3" s="263" t="s">
+      <c r="I3" s="276"/>
+      <c r="J3" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="305" t="s">
+      <c r="K3" s="279" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="20" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A4" s="359"/>
-      <c r="B4" s="294"/>
-      <c r="C4" s="297"/>
-      <c r="D4" s="298"/>
-      <c r="E4" s="297"/>
-      <c r="F4" s="298"/>
-      <c r="G4" s="300"/>
-      <c r="H4" s="361"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="306"/>
+      <c r="A4" s="368"/>
+      <c r="B4" s="268"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="272"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="272"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="370"/>
+      <c r="I4" s="278"/>
+      <c r="J4" s="300"/>
+      <c r="K4" s="280"/>
     </row>
     <row r="5" spans="1:11" ht="31.2">
       <c r="A5" s="218" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="272" t="s">
+      <c r="B5" s="281" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="282">
+      <c r="C5" s="292">
         <v>1</v>
       </c>
-      <c r="D5" s="277" t="s">
+      <c r="D5" s="286" t="s">
         <v>208</v>
       </c>
       <c r="E5" s="163">
@@ -21317,9 +21317,9 @@
       <c r="A6" s="218" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="273"/>
-      <c r="C6" s="362"/>
-      <c r="D6" s="278"/>
+      <c r="B6" s="282"/>
+      <c r="C6" s="365"/>
+      <c r="D6" s="287"/>
       <c r="E6" s="21"/>
       <c r="F6" s="167"/>
       <c r="G6" s="168"/>
@@ -21334,11 +21334,11 @@
       <c r="A7" s="218" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="273"/>
-      <c r="C7" s="363">
+      <c r="B7" s="282"/>
+      <c r="C7" s="366">
         <v>2</v>
       </c>
-      <c r="D7" s="265" t="s">
+      <c r="D7" s="289" t="s">
         <v>303</v>
       </c>
       <c r="E7" s="21">
@@ -21365,9 +21365,9 @@
     </row>
     <row r="8" spans="1:11" ht="33" customHeight="1">
       <c r="A8" s="218"/>
-      <c r="B8" s="273"/>
-      <c r="C8" s="363"/>
-      <c r="D8" s="265"/>
+      <c r="B8" s="282"/>
+      <c r="C8" s="366"/>
+      <c r="D8" s="289"/>
       <c r="E8" s="21">
         <v>2</v>
       </c>
@@ -21392,9 +21392,9 @@
     </row>
     <row r="9" spans="1:11" ht="39.6" customHeight="1">
       <c r="A9" s="218"/>
-      <c r="B9" s="273"/>
-      <c r="C9" s="363"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="366"/>
+      <c r="D9" s="289"/>
       <c r="E9" s="21">
         <v>3</v>
       </c>
@@ -21417,9 +21417,9 @@
     </row>
     <row r="10" spans="1:11" ht="29.4" customHeight="1">
       <c r="A10" s="218"/>
-      <c r="B10" s="273"/>
-      <c r="C10" s="363"/>
-      <c r="D10" s="265"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="366"/>
+      <c r="D10" s="289"/>
       <c r="E10" s="21">
         <v>4</v>
       </c>
@@ -21442,9 +21442,9 @@
     </row>
     <row r="11" spans="1:11" ht="42" customHeight="1">
       <c r="A11" s="218"/>
-      <c r="B11" s="273"/>
-      <c r="C11" s="363"/>
-      <c r="D11" s="265"/>
+      <c r="B11" s="282"/>
+      <c r="C11" s="366"/>
+      <c r="D11" s="289"/>
       <c r="E11" s="21">
         <v>5</v>
       </c>
@@ -21469,9 +21469,9 @@
       <c r="A12" s="218" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="273"/>
-      <c r="C12" s="363"/>
-      <c r="D12" s="265"/>
+      <c r="B12" s="282"/>
+      <c r="C12" s="366"/>
+      <c r="D12" s="289"/>
       <c r="E12" s="21">
         <v>6</v>
       </c>
@@ -21488,11 +21488,11 @@
       <c r="A13" s="218" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="273"/>
-      <c r="C13" s="364">
+      <c r="B13" s="282"/>
+      <c r="C13" s="361">
         <v>9</v>
       </c>
-      <c r="D13" s="265" t="s">
+      <c r="D13" s="289" t="s">
         <v>210</v>
       </c>
       <c r="E13" s="21">
@@ -21517,9 +21517,9 @@
     </row>
     <row r="14" spans="1:11" ht="39.6">
       <c r="A14" s="218"/>
-      <c r="B14" s="273"/>
-      <c r="C14" s="364"/>
-      <c r="D14" s="265"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="361"/>
+      <c r="D14" s="289"/>
       <c r="E14" s="21">
         <v>2</v>
       </c>
@@ -21542,9 +21542,9 @@
     </row>
     <row r="15" spans="1:11" ht="25.2" customHeight="1">
       <c r="A15" s="218"/>
-      <c r="B15" s="273"/>
-      <c r="C15" s="364"/>
-      <c r="D15" s="265"/>
+      <c r="B15" s="282"/>
+      <c r="C15" s="361"/>
+      <c r="D15" s="289"/>
       <c r="E15" s="21"/>
       <c r="F15" s="167"/>
       <c r="G15" s="168"/>
@@ -21557,11 +21557,11 @@
       <c r="A16" s="218" t="s">
         <v>205</v>
       </c>
-      <c r="B16" s="273"/>
-      <c r="C16" s="364">
+      <c r="B16" s="282"/>
+      <c r="C16" s="361">
         <v>10</v>
       </c>
-      <c r="D16" s="265" t="s">
+      <c r="D16" s="289" t="s">
         <v>211</v>
       </c>
       <c r="E16" s="21">
@@ -21588,9 +21588,9 @@
       <c r="A17" s="218" t="s">
         <v>205</v>
       </c>
-      <c r="B17" s="273"/>
-      <c r="C17" s="364"/>
-      <c r="D17" s="265"/>
+      <c r="B17" s="282"/>
+      <c r="C17" s="361"/>
+      <c r="D17" s="289"/>
       <c r="E17" s="21"/>
       <c r="F17" s="167"/>
       <c r="G17" s="168"/>
@@ -21607,9 +21607,9 @@
     </row>
     <row r="18" spans="1:11" ht="25.2" customHeight="1">
       <c r="A18" s="218"/>
-      <c r="B18" s="273"/>
-      <c r="C18" s="364"/>
-      <c r="D18" s="265"/>
+      <c r="B18" s="282"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="289"/>
       <c r="E18" s="21"/>
       <c r="F18" s="167"/>
       <c r="G18" s="168"/>
@@ -21619,14 +21619,12 @@
       <c r="K18" s="170"/>
     </row>
     <row r="19" spans="1:11" ht="29.4" customHeight="1">
-      <c r="A19" s="218" t="s">
-        <v>204</v>
-      </c>
-      <c r="B19" s="273"/>
-      <c r="C19" s="364">
+      <c r="A19" s="218"/>
+      <c r="B19" s="282"/>
+      <c r="C19" s="361">
         <v>11</v>
       </c>
-      <c r="D19" s="265" t="s">
+      <c r="D19" s="289" t="s">
         <v>212</v>
       </c>
       <c r="E19" s="240">
@@ -21645,9 +21643,9 @@
     </row>
     <row r="20" spans="1:11" ht="37.799999999999997" customHeight="1">
       <c r="A20" s="218"/>
-      <c r="B20" s="273"/>
-      <c r="C20" s="364"/>
-      <c r="D20" s="265"/>
+      <c r="B20" s="282"/>
+      <c r="C20" s="361"/>
+      <c r="D20" s="289"/>
       <c r="E20" s="240"/>
       <c r="F20" s="241" t="s">
         <v>239</v>
@@ -21666,9 +21664,9 @@
     </row>
     <row r="21" spans="1:11" ht="29.4" customHeight="1">
       <c r="A21" s="218"/>
-      <c r="B21" s="273"/>
-      <c r="C21" s="364"/>
-      <c r="D21" s="265"/>
+      <c r="B21" s="282"/>
+      <c r="C21" s="361"/>
+      <c r="D21" s="289"/>
       <c r="E21" s="240"/>
       <c r="F21" s="241"/>
       <c r="G21" s="242"/>
@@ -21685,9 +21683,9 @@
     </row>
     <row r="22" spans="1:11" ht="87" customHeight="1">
       <c r="A22" s="218"/>
-      <c r="B22" s="273"/>
-      <c r="C22" s="364"/>
-      <c r="D22" s="265"/>
+      <c r="B22" s="282"/>
+      <c r="C22" s="361"/>
+      <c r="D22" s="289"/>
       <c r="E22" s="240"/>
       <c r="F22" s="241"/>
       <c r="G22" s="242"/>
@@ -21704,9 +21702,9 @@
     </row>
     <row r="23" spans="1:11" ht="29.4" customHeight="1">
       <c r="A23" s="218"/>
-      <c r="B23" s="273"/>
-      <c r="C23" s="364"/>
-      <c r="D23" s="265"/>
+      <c r="B23" s="282"/>
+      <c r="C23" s="361"/>
+      <c r="D23" s="289"/>
       <c r="E23" s="240">
         <v>2</v>
       </c>
@@ -21727,9 +21725,9 @@
     </row>
     <row r="24" spans="1:11" ht="29.4" customHeight="1">
       <c r="A24" s="218"/>
-      <c r="B24" s="273"/>
-      <c r="C24" s="364"/>
-      <c r="D24" s="265"/>
+      <c r="B24" s="282"/>
+      <c r="C24" s="361"/>
+      <c r="D24" s="289"/>
       <c r="E24" s="240"/>
       <c r="F24" s="241"/>
       <c r="G24" s="242"/>
@@ -21746,9 +21744,9 @@
     </row>
     <row r="25" spans="1:11" ht="31.2">
       <c r="A25" s="218"/>
-      <c r="B25" s="273"/>
-      <c r="C25" s="364"/>
-      <c r="D25" s="265"/>
+      <c r="B25" s="282"/>
+      <c r="C25" s="361"/>
+      <c r="D25" s="289"/>
       <c r="E25" s="240"/>
       <c r="F25" s="241"/>
       <c r="G25" s="242"/>
@@ -21765,9 +21763,9 @@
     </row>
     <row r="26" spans="1:11" ht="25.2" customHeight="1">
       <c r="A26" s="218"/>
-      <c r="B26" s="273"/>
-      <c r="C26" s="364"/>
-      <c r="D26" s="265"/>
+      <c r="B26" s="282"/>
+      <c r="C26" s="361"/>
+      <c r="D26" s="289"/>
       <c r="E26" s="240">
         <v>3</v>
       </c>
@@ -21788,9 +21786,9 @@
     </row>
     <row r="27" spans="1:11" ht="25.2" customHeight="1">
       <c r="A27" s="218"/>
-      <c r="B27" s="273"/>
-      <c r="C27" s="364"/>
-      <c r="D27" s="265"/>
+      <c r="B27" s="282"/>
+      <c r="C27" s="361"/>
+      <c r="D27" s="289"/>
       <c r="E27" s="240"/>
       <c r="F27" s="241"/>
       <c r="G27" s="242"/>
@@ -21805,9 +21803,9 @@
     </row>
     <row r="28" spans="1:11" ht="25.2" customHeight="1">
       <c r="A28" s="218"/>
-      <c r="B28" s="273"/>
-      <c r="C28" s="364"/>
-      <c r="D28" s="265"/>
+      <c r="B28" s="282"/>
+      <c r="C28" s="361"/>
+      <c r="D28" s="289"/>
       <c r="E28" s="240"/>
       <c r="F28" s="241"/>
       <c r="G28" s="242"/>
@@ -21822,9 +21820,9 @@
     </row>
     <row r="29" spans="1:11" ht="25.2" customHeight="1">
       <c r="A29" s="218"/>
-      <c r="B29" s="273"/>
-      <c r="C29" s="364"/>
-      <c r="D29" s="265"/>
+      <c r="B29" s="282"/>
+      <c r="C29" s="361"/>
+      <c r="D29" s="289"/>
       <c r="E29" s="240"/>
       <c r="F29" s="241"/>
       <c r="G29" s="242"/>
@@ -21839,9 +21837,9 @@
     </row>
     <row r="30" spans="1:11" ht="25.2" customHeight="1">
       <c r="A30" s="218"/>
-      <c r="B30" s="273"/>
-      <c r="C30" s="364"/>
-      <c r="D30" s="265"/>
+      <c r="B30" s="282"/>
+      <c r="C30" s="361"/>
+      <c r="D30" s="289"/>
       <c r="E30" s="21">
         <v>4</v>
       </c>
@@ -21862,9 +21860,9 @@
     </row>
     <row r="31" spans="1:11" ht="25.2" customHeight="1">
       <c r="A31" s="218"/>
-      <c r="B31" s="273"/>
-      <c r="C31" s="364"/>
-      <c r="D31" s="265"/>
+      <c r="B31" s="282"/>
+      <c r="C31" s="361"/>
+      <c r="D31" s="289"/>
       <c r="E31" s="21"/>
       <c r="F31" s="167"/>
       <c r="G31" s="168"/>
@@ -21879,9 +21877,9 @@
     </row>
     <row r="32" spans="1:11" ht="25.2" customHeight="1">
       <c r="A32" s="218"/>
-      <c r="B32" s="273"/>
-      <c r="C32" s="364"/>
-      <c r="D32" s="265"/>
+      <c r="B32" s="282"/>
+      <c r="C32" s="361"/>
+      <c r="D32" s="289"/>
       <c r="E32" s="21"/>
       <c r="F32" s="167"/>
       <c r="G32" s="168"/>
@@ -21896,9 +21894,9 @@
     </row>
     <row r="33" spans="1:11" ht="25.2" customHeight="1">
       <c r="A33" s="218"/>
-      <c r="B33" s="273"/>
-      <c r="C33" s="364"/>
-      <c r="D33" s="265"/>
+      <c r="B33" s="282"/>
+      <c r="C33" s="361"/>
+      <c r="D33" s="289"/>
       <c r="E33" s="21"/>
       <c r="F33" s="167"/>
       <c r="G33" s="168"/>
@@ -21913,9 +21911,9 @@
     </row>
     <row r="34" spans="1:11" ht="25.2" customHeight="1">
       <c r="A34" s="218"/>
-      <c r="B34" s="273"/>
-      <c r="C34" s="364"/>
-      <c r="D34" s="265"/>
+      <c r="B34" s="282"/>
+      <c r="C34" s="361"/>
+      <c r="D34" s="289"/>
       <c r="E34" s="21"/>
       <c r="F34" s="167"/>
       <c r="G34" s="168"/>
@@ -21930,9 +21928,9 @@
     </row>
     <row r="35" spans="1:11" ht="55.2" customHeight="1">
       <c r="A35" s="218"/>
-      <c r="B35" s="273"/>
-      <c r="C35" s="364"/>
-      <c r="D35" s="265"/>
+      <c r="B35" s="282"/>
+      <c r="C35" s="361"/>
+      <c r="D35" s="289"/>
       <c r="E35" s="21">
         <v>5</v>
       </c>
@@ -21953,11 +21951,11 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="31.2">
+    <row r="36" spans="1:11" ht="19.8">
       <c r="A36" s="218"/>
-      <c r="B36" s="273"/>
-      <c r="C36" s="364"/>
-      <c r="D36" s="265"/>
+      <c r="B36" s="282"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="289"/>
       <c r="E36" s="21"/>
       <c r="F36" s="167"/>
       <c r="G36" s="168"/>
@@ -21974,9 +21972,9 @@
     </row>
     <row r="37" spans="1:11" ht="25.2" customHeight="1">
       <c r="A37" s="218"/>
-      <c r="B37" s="273"/>
-      <c r="C37" s="364"/>
-      <c r="D37" s="265"/>
+      <c r="B37" s="282"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="289"/>
       <c r="E37" s="21">
         <v>6</v>
       </c>
@@ -21995,9 +21993,9 @@
     </row>
     <row r="38" spans="1:11" ht="25.2" customHeight="1">
       <c r="A38" s="218"/>
-      <c r="B38" s="273"/>
-      <c r="C38" s="364"/>
-      <c r="D38" s="265"/>
+      <c r="B38" s="282"/>
+      <c r="C38" s="361"/>
+      <c r="D38" s="289"/>
       <c r="E38" s="21"/>
       <c r="F38" s="167"/>
       <c r="G38" s="168"/>
@@ -22012,9 +22010,9 @@
     </row>
     <row r="39" spans="1:11" ht="25.2" customHeight="1">
       <c r="A39" s="218"/>
-      <c r="B39" s="273"/>
-      <c r="C39" s="364"/>
-      <c r="D39" s="265"/>
+      <c r="B39" s="282"/>
+      <c r="C39" s="361"/>
+      <c r="D39" s="289"/>
       <c r="E39" s="21"/>
       <c r="F39" s="167"/>
       <c r="G39" s="168"/>
@@ -22029,9 +22027,9 @@
     </row>
     <row r="40" spans="1:11" ht="84" customHeight="1">
       <c r="A40" s="218"/>
-      <c r="B40" s="273"/>
-      <c r="C40" s="364"/>
-      <c r="D40" s="265"/>
+      <c r="B40" s="282"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="289"/>
       <c r="E40" s="21">
         <v>7</v>
       </c>
@@ -22054,11 +22052,11 @@
     </row>
     <row r="41" spans="1:11" ht="45" customHeight="1">
       <c r="A41" s="218"/>
-      <c r="B41" s="273"/>
-      <c r="C41" s="364">
+      <c r="B41" s="282"/>
+      <c r="C41" s="361">
         <v>13</v>
       </c>
-      <c r="D41" s="265" t="s">
+      <c r="D41" s="289" t="s">
         <v>304</v>
       </c>
       <c r="E41" s="21">
@@ -22085,9 +22083,9 @@
     </row>
     <row r="42" spans="1:11" ht="45" customHeight="1">
       <c r="A42" s="218"/>
-      <c r="B42" s="273"/>
-      <c r="C42" s="364"/>
-      <c r="D42" s="265"/>
+      <c r="B42" s="282"/>
+      <c r="C42" s="361"/>
+      <c r="D42" s="289"/>
       <c r="E42" s="21">
         <v>2</v>
       </c>
@@ -22112,11 +22110,11 @@
     </row>
     <row r="43" spans="1:11" ht="40.200000000000003" thickBot="1">
       <c r="A43" s="220"/>
-      <c r="B43" s="273"/>
-      <c r="C43" s="364">
+      <c r="B43" s="282"/>
+      <c r="C43" s="361">
         <v>14</v>
       </c>
-      <c r="D43" s="265" t="s">
+      <c r="D43" s="289" t="s">
         <v>213</v>
       </c>
       <c r="E43" s="21">
@@ -22141,9 +22139,9 @@
     </row>
     <row r="44" spans="1:11" ht="19.8">
       <c r="A44" s="221"/>
-      <c r="B44" s="273"/>
-      <c r="C44" s="364"/>
-      <c r="D44" s="265"/>
+      <c r="B44" s="282"/>
+      <c r="C44" s="361"/>
+      <c r="D44" s="289"/>
       <c r="E44" s="21"/>
       <c r="F44" s="167"/>
       <c r="G44" s="168"/>
@@ -22160,9 +22158,9 @@
     </row>
     <row r="45" spans="1:11" ht="31.2">
       <c r="A45" s="218"/>
-      <c r="B45" s="273"/>
-      <c r="C45" s="364"/>
-      <c r="D45" s="265"/>
+      <c r="B45" s="282"/>
+      <c r="C45" s="361"/>
+      <c r="D45" s="289"/>
       <c r="E45" s="21"/>
       <c r="F45" s="167"/>
       <c r="G45" s="168"/>
@@ -22179,9 +22177,9 @@
     </row>
     <row r="46" spans="1:11" ht="25.2" customHeight="1">
       <c r="A46" s="218"/>
-      <c r="B46" s="273"/>
-      <c r="C46" s="364"/>
-      <c r="D46" s="265"/>
+      <c r="B46" s="282"/>
+      <c r="C46" s="361"/>
+      <c r="D46" s="289"/>
       <c r="E46" s="21">
         <v>2</v>
       </c>
@@ -22204,9 +22202,9 @@
     </row>
     <row r="47" spans="1:11" ht="25.2" customHeight="1">
       <c r="A47" s="218"/>
-      <c r="B47" s="273"/>
-      <c r="C47" s="364"/>
-      <c r="D47" s="265"/>
+      <c r="B47" s="282"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="289"/>
       <c r="E47" s="21"/>
       <c r="F47" s="167"/>
       <c r="G47" s="168"/>
@@ -22217,11 +22215,11 @@
     </row>
     <row r="48" spans="1:11" ht="39.6">
       <c r="A48" s="218"/>
-      <c r="B48" s="273"/>
-      <c r="C48" s="364">
+      <c r="B48" s="282"/>
+      <c r="C48" s="361">
         <v>16</v>
       </c>
-      <c r="D48" s="265" t="s">
+      <c r="D48" s="289" t="s">
         <v>214</v>
       </c>
       <c r="E48" s="21">
@@ -22246,9 +22244,9 @@
     </row>
     <row r="49" spans="1:11" ht="25.2" customHeight="1">
       <c r="A49" s="218"/>
-      <c r="B49" s="273"/>
-      <c r="C49" s="364"/>
-      <c r="D49" s="265"/>
+      <c r="B49" s="282"/>
+      <c r="C49" s="361"/>
+      <c r="D49" s="289"/>
       <c r="E49" s="21"/>
       <c r="F49" s="167"/>
       <c r="G49" s="168"/>
@@ -22259,11 +22257,11 @@
     </row>
     <row r="50" spans="1:11" ht="25.2" customHeight="1">
       <c r="A50" s="218"/>
-      <c r="B50" s="273"/>
-      <c r="C50" s="368">
+      <c r="B50" s="282"/>
+      <c r="C50" s="362">
         <v>19</v>
       </c>
-      <c r="D50" s="368" t="s">
+      <c r="D50" s="362" t="s">
         <v>215</v>
       </c>
       <c r="E50" s="193">
@@ -22286,9 +22284,9 @@
     </row>
     <row r="51" spans="1:11" ht="25.2" customHeight="1">
       <c r="A51" s="218"/>
-      <c r="B51" s="273"/>
-      <c r="C51" s="369"/>
-      <c r="D51" s="369"/>
+      <c r="B51" s="282"/>
+      <c r="C51" s="363"/>
+      <c r="D51" s="363"/>
       <c r="E51" s="193"/>
       <c r="F51" s="198"/>
       <c r="G51" s="195"/>
@@ -22299,15 +22297,15 @@
       <c r="J51" s="197" t="s">
         <v>264</v>
       </c>
-      <c r="K51" s="365" t="s">
+      <c r="K51" s="358" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="25.2" customHeight="1">
       <c r="A52" s="218"/>
-      <c r="B52" s="273"/>
-      <c r="C52" s="369"/>
-      <c r="D52" s="369"/>
+      <c r="B52" s="282"/>
+      <c r="C52" s="363"/>
+      <c r="D52" s="363"/>
       <c r="E52" s="193"/>
       <c r="F52" s="198"/>
       <c r="G52" s="195"/>
@@ -22318,13 +22316,13 @@
       <c r="J52" s="197" t="s">
         <v>265</v>
       </c>
-      <c r="K52" s="366"/>
+      <c r="K52" s="359"/>
     </row>
     <row r="53" spans="1:11" ht="25.2" customHeight="1">
       <c r="A53" s="218"/>
-      <c r="B53" s="273"/>
-      <c r="C53" s="369"/>
-      <c r="D53" s="369"/>
+      <c r="B53" s="282"/>
+      <c r="C53" s="363"/>
+      <c r="D53" s="363"/>
       <c r="E53" s="193"/>
       <c r="F53" s="198"/>
       <c r="G53" s="195"/>
@@ -22335,13 +22333,13 @@
       <c r="J53" s="197" t="s">
         <v>266</v>
       </c>
-      <c r="K53" s="366"/>
+      <c r="K53" s="359"/>
     </row>
     <row r="54" spans="1:11" ht="31.2" customHeight="1">
       <c r="A54" s="218"/>
-      <c r="B54" s="273"/>
-      <c r="C54" s="369"/>
-      <c r="D54" s="369"/>
+      <c r="B54" s="282"/>
+      <c r="C54" s="363"/>
+      <c r="D54" s="363"/>
       <c r="E54" s="199"/>
       <c r="F54" s="200"/>
       <c r="G54" s="201"/>
@@ -22352,13 +22350,13 @@
       <c r="J54" s="202" t="s">
         <v>301</v>
       </c>
-      <c r="K54" s="367"/>
+      <c r="K54" s="360"/>
     </row>
     <row r="55" spans="1:11" ht="24" customHeight="1" thickBot="1">
       <c r="A55" s="219"/>
-      <c r="B55" s="274"/>
-      <c r="C55" s="370"/>
-      <c r="D55" s="370"/>
+      <c r="B55" s="283"/>
+      <c r="C55" s="364"/>
+      <c r="D55" s="364"/>
       <c r="E55" s="203"/>
       <c r="F55" s="204"/>
       <c r="G55" s="205"/>
@@ -22371,6 +22369,25 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:B55"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="D7:D12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C16:C18"/>
     <mergeCell ref="K51:K54"/>
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="C19:C40"/>
@@ -22383,25 +22400,6 @@
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="C50:C55"/>
     <mergeCell ref="D50:D55"/>
-    <mergeCell ref="B5:B55"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="D7:D12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="41" orientation="portrait" r:id="rId1"/>
@@ -22415,11 +22413,11 @@
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="128" style="223" customWidth="1"/>
-    <col min="3" max="3" width="5.77734375" customWidth="1"/>
-    <col min="4" max="4" width="53.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.796875" customWidth="1"/>
+    <col min="4" max="4" width="53.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="36" customHeight="1">
@@ -22427,7 +22425,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="2:4" ht="45.6">
+    <row r="2" spans="2:4" ht="22.8">
       <c r="B2" s="222" t="s">
         <v>313</v>
       </c>
@@ -22575,9 +22573,9 @@
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:B41"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="105.21875" style="223" customWidth="1"/>
+    <col min="2" max="2" width="105.19921875" style="223" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" ht="43.2" customHeight="1">
@@ -22662,7 +22660,7 @@
     <row r="20" spans="2:2">
       <c r="B20" s="226"/>
     </row>
-    <row r="21" spans="2:2" ht="42">
+    <row r="21" spans="2:2" ht="28.2">
       <c r="B21" s="227" t="s">
         <v>395</v>
       </c>
@@ -22675,12 +22673,12 @@
         <v>328</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="27.6">
+    <row r="24" spans="2:2">
       <c r="B24" s="227" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="42.6">
+    <row r="25" spans="2:2" ht="42">
       <c r="B25" s="227" t="s">
         <v>340</v>
       </c>
@@ -22699,7 +22697,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="41.4">
+    <row r="30" spans="2:2" ht="27.6">
       <c r="B30" s="224" t="s">
         <v>396</v>
       </c>
@@ -22764,9 +22762,9 @@
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:B71"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="108.44140625" style="223" customWidth="1"/>
+    <col min="2" max="2" width="108.3984375" style="223" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" ht="34.799999999999997" customHeight="1">
@@ -22774,12 +22772,12 @@
         <v>393</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="43.2">
+    <row r="2" spans="2:2" ht="41.4">
       <c r="B2" s="223" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="23.4">
+    <row r="4" spans="2:2" ht="22.2">
       <c r="B4" s="231" t="s">
         <v>346</v>
       </c>
@@ -22797,7 +22795,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="28.8">
+    <row r="8" spans="2:2" ht="27.6">
       <c r="B8" s="232" t="s">
         <v>348</v>
       </c>
@@ -22807,7 +22805,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="23.4">
+    <row r="22" spans="2:2" ht="22.2">
       <c r="B22" s="230" t="s">
         <v>350</v>
       </c>
@@ -22815,7 +22813,7 @@
     <row r="23" spans="2:2" ht="8.4" customHeight="1">
       <c r="B23"/>
     </row>
-    <row r="24" spans="2:2" ht="18">
+    <row r="24" spans="2:2" ht="17.399999999999999">
       <c r="B24" s="235" t="s">
         <v>351</v>
       </c>
@@ -22845,7 +22843,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="18">
+    <row r="31" spans="2:2" ht="17.399999999999999">
       <c r="B31" s="234" t="s">
         <v>358</v>
       </c>
@@ -22905,12 +22903,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="15.6">
+    <row r="58" spans="2:2" ht="15">
       <c r="B58" s="237" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="28.8">
+    <row r="59" spans="2:2" ht="27.6">
       <c r="B59" s="232" t="s">
         <v>375</v>
       </c>
@@ -22930,12 +22928,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="63" spans="2:2" ht="28.8">
+    <row r="63" spans="2:2" ht="27.6">
       <c r="B63" s="226" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="64" spans="2:2" ht="28.8">
+    <row r="64" spans="2:2" ht="27.6">
       <c r="B64" s="226" t="s">
         <v>380</v>
       </c>
@@ -22945,7 +22943,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="67" spans="2:2" ht="18">
+    <row r="67" spans="2:2" ht="17.399999999999999">
       <c r="B67" s="235" t="s">
         <v>371</v>
       </c>
@@ -22955,7 +22953,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="69" spans="2:2" ht="43.2">
+    <row r="69" spans="2:2" ht="41.4">
       <c r="B69" s="232" t="s">
         <v>373</v>
       </c>
